--- a/docs/planning/ERD_6기_5팀_v1.3.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.3.xlsx
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">

--- a/docs/planning/ERD_6기_5팀_v1.3.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.3.xlsx
@@ -3957,7 +3957,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6895,6 +6895,25 @@
         </is>
       </c>
       <c r="E152" s="10" t="n"/>
+    </row>
+    <row r="153" hidden="1" outlineLevel="1">
+      <c r="A153" s="10" t="n"/>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>파일 머리말 · 챗봇 영역 설명 (dbml)</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>기준 "Figma 통합 와이어프레임(53개 화면)" · 4. 챗봇 영역 "화면 CB-01 ~ CB-05-E1"</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>기준 "Figma 통합 와이어프레임(50개 화면)" · "화면 CB-01 ~ CB-05" — 키보드 받아쓰기로 바뀌어 CB-05-E1 · CB-05-P · CB-05-E2 삭제 (10/6 수인 #50). 테이블 · 칸은 바뀌지 않음</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/docs/planning/ERD_6기_5팀_v1.3.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.3.xlsx
@@ -20,12 +20,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'사용자'!$A$4:$N$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'입력'!$A$4:$N$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'입력'!$A$4:$N$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'분석'!$A$4:$N$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'챗봇'!$A$4:$N$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'실천·보상'!$A$4:$N$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'마스터'!$A$4:$N$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FHIR 대응'!$A$5:$H$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FHIR 대응'!$A$5:$H$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2155,132 +2155,128 @@
       <c r="H36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>guidance</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.dosageInstruction.patientInstruction</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>문장 목록 → 줄바꿈으로 이어 붙인 text</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>match_status · match_score</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr"/>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr"/>
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>약품 매칭 상태는 내부 처리 정보</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="34" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B38" s="40" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>prescription_item_candidates</t>
         </is>
       </c>
-      <c r="C38" s="36" t="inlineStr">
+      <c r="C39" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="36" t="inlineStr">
+      <c r="E39" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="36" t="inlineStr"/>
-      <c r="G38" s="34" t="inlineStr">
+      <c r="F39" s="36" t="inlineStr"/>
+      <c r="G39" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H38" s="36" t="inlineStr">
+      <c r="H39" s="36" t="inlineStr">
         <is>
           <t>약품 매칭 후보 (내부 처리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>health_checkups · checkup_results</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>DiagnosticReport · Observation</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>Observation.code / valueQuantity</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>검진 항목 코드 → Observation.code</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="inlineStr">
-        <is>
-          <t>보류 (REQ-015)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>analyses</t>
+          <t>health_checkups · checkup_results</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -2290,17 +2286,17 @@
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>DiagnosticReport · Observation</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Observation.code / valueQuantity</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>분석 작업 1건 = Task 1개</t>
+          <t>검진 항목 코드 → Observation.code</t>
         </is>
       </c>
       <c r="G40" s="16" t="inlineStr">
@@ -2310,7 +2306,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>비동기 작업 상태를 Task로 표현</t>
+          <t>보류 (REQ-015)</t>
         </is>
       </c>
     </row>
@@ -2320,149 +2316,149 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B41" s="33" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>분석 작업 1건 = Task 1개</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>비동기 작업 상태를 Task로 표현</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Task.status</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G42" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H41" s="15" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="H42" s="15" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B42" s="37" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
-      <c r="C42" s="21" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>current_step · failed_step · retry_count · error_code</t>
         </is>
       </c>
-      <c r="D42" s="21" t="inlineStr">
+      <c r="D43" s="21" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E42" s="21" t="inlineStr">
+      <c r="E43" s="21" t="inlineStr">
         <is>
           <t>Task.businessStatus · Task.statusReason</t>
         </is>
       </c>
-      <c r="F42" s="21" t="inlineStr"/>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="F43" s="21" t="inlineStr"/>
+      <c r="G43" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H42" s="21" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="H43" s="21" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B43" s="35" t="inlineStr">
+      <c r="B44" s="35" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
-      <c r="C43" s="36" t="inlineStr">
+      <c r="C44" s="36" t="inlineStr">
         <is>
           <t>user_birth_year</t>
         </is>
       </c>
-      <c r="D43" s="36" t="inlineStr">
+      <c r="D44" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E43" s="36" t="inlineStr">
+      <c r="E44" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="36" t="inlineStr"/>
-      <c r="G43" s="34" t="inlineStr">
+      <c r="F44" s="36" t="inlineStr"/>
+      <c r="G44" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H43" s="36" t="inlineStr">
+      <c r="H44" s="36" t="inlineStr">
         <is>
           <t>분석 시점 스냅샷 (내부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>analysis_prescriptions</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>Task.input</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
-        <is>
-          <t>valueReference = MedicationRequest</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="inlineStr">
-        <is>
-          <t>분석에 넣은 처방 목록</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2470,7 @@
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>analysis_diseases</t>
+          <t>analysis_prescriptions</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
@@ -2484,21 +2480,29 @@
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr"/>
+          <t>Task.input</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>valueReference = MedicationRequest</t>
+        </is>
+      </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H45" s="15" t="inlineStr"/>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>분석에 넣은 처방 목록</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -2506,123 +2510,115 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B46" s="33" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>analysis_diseases</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr"/>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B47" s="33" t="inlineStr">
+        <is>
+          <t>analysis_diseases</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
           <t>origin</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>Condition.asserter</t>
         </is>
       </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="F47" s="15" t="inlineStr">
         <is>
           <t>prescription → 처방전에서 옴 / user → asserter = Patient (직접 선택)</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="G47" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H46" s="15" t="inlineStr">
+      <c r="H47" s="15" t="inlineStr">
         <is>
           <t>누가 주장한 질환인지 구분</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="30" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B47" s="38" t="inlineStr">
+      <c r="B48" s="38" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C47" s="32" t="inlineStr">
+      <c r="C48" s="32" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D47" s="39" t="inlineStr">
+      <c r="D48" s="39" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E47" s="32" t="inlineStr">
+      <c r="E48" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="F47" s="32" t="inlineStr">
+      <c r="F48" s="32" t="inlineStr">
         <is>
           <t>경고 1건 = DetectedIssue 1개</t>
         </is>
       </c>
-      <c r="G47" s="30" t="inlineStr">
+      <c r="G48" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H47" s="32" t="inlineStr">
+      <c r="H48" s="32" t="inlineStr">
         <is>
           <t>FHIR에 "약물 문제 감지" 전용 리소스가 있음 — 가장 잘 맞는 부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B48" s="33" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>warning_type</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue.code</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="inlineStr">
-        <is>
-          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="inlineStr">
-        <is>
-          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
         </is>
       </c>
     </row>
@@ -2639,68 +2635,72 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
+          <t>warning_type</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue.code</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue.severity</t>
         </is>
       </c>
-      <c r="F49" s="15" t="inlineStr">
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>danger → high / caution → moderate / info → low</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
+      <c r="G50" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H49" s="15" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="30" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B50" s="31" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="C50" s="32" t="inlineStr">
-        <is>
-          <t>item_id_a · item_id_b</t>
-        </is>
-      </c>
-      <c r="D50" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="E50" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue.implicated</t>
-        </is>
-      </c>
-      <c r="F50" s="32" t="inlineStr">
-        <is>
-          <t>Reference(MedicationRequest) 2개</t>
-        </is>
-      </c>
-      <c r="G50" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H50" s="32" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="30" t="inlineStr">
@@ -2715,142 +2715,142 @@
       </c>
       <c r="C51" s="32" t="inlineStr">
         <is>
+          <t>item_id_a · item_id_b</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E51" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue.implicated</t>
+        </is>
+      </c>
+      <c r="F51" s="32" t="inlineStr">
+        <is>
+          <t>Reference(MedicationRequest) 2개</t>
+        </is>
+      </c>
+      <c r="G51" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H51" s="32" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="D51" s="32" t="inlineStr">
+      <c r="D52" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E51" s="32" t="inlineStr">
+      <c r="E52" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue.detail</t>
         </is>
       </c>
-      <c r="F51" s="32" t="inlineStr">
+      <c r="F52" s="32" t="inlineStr">
         <is>
           <t>DUR 금기 사유 원문</t>
         </is>
       </c>
-      <c r="G51" s="30" t="inlineStr">
+      <c r="G52" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H51" s="32" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="H52" s="32" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B52" s="33" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>source · notice_date</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue.reference</t>
         </is>
       </c>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="F53" s="15" t="inlineStr">
         <is>
           <t>식약처 고시 출처</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
+      <c r="G53" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H52" s="15" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="H53" s="15" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B53" s="37" t="inlineStr">
+      <c r="B54" s="37" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C53" s="21" t="inlineStr">
+      <c r="C54" s="21" t="inlineStr">
         <is>
           <t>summary · daily_total · max_daily</t>
         </is>
       </c>
-      <c r="D53" s="21" t="inlineStr">
+      <c r="D54" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E54" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F53" s="21" t="inlineStr"/>
-      <c r="G53" s="22" t="inlineStr">
+      <c r="F54" s="21" t="inlineStr"/>
+      <c r="G54" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H53" s="21" t="inlineStr">
+      <c r="H54" s="21" t="inlineStr">
         <is>
           <t>화면 문장 · 용량 계산값</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="34" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B54" s="40" t="inlineStr">
-        <is>
-          <t>guides</t>
-        </is>
-      </c>
-      <c r="C54" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E54" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="36" t="inlineStr"/>
-      <c r="G54" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H54" s="36" t="inlineStr">
-        <is>
-          <t>AI 생성 안내문 (의료 기록 아님). 필요하면 DocumentReference로 보관</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B55" s="40" t="inlineStr">
         <is>
-          <t>feedbacks</t>
+          <t>guides</t>
         </is>
       </c>
       <c r="C55" s="36" t="inlineStr">
@@ -2888,19 +2888,19 @@
       </c>
       <c r="H55" s="36" t="inlineStr">
         <is>
-          <t>서비스 피드백</t>
+          <t>AI 생성 안내문 (의료 기록 아님). 필요하면 DocumentReference로 보관</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>챗봇</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B56" s="40" t="inlineStr">
         <is>
-          <t>chat_sessions</t>
+          <t>feedbacks</t>
         </is>
       </c>
       <c r="C56" s="36" t="inlineStr">
@@ -2926,45 +2926,45 @@
       </c>
       <c r="H56" s="36" t="inlineStr">
         <is>
+          <t>서비스 피드백</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>챗봇</t>
+        </is>
+      </c>
+      <c r="B57" s="40" t="inlineStr">
+        <is>
+          <t>chat_sessions</t>
+        </is>
+      </c>
+      <c r="C57" s="36" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="36" t="inlineStr"/>
+      <c r="G57" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H57" s="36" t="inlineStr">
+        <is>
           <t>대화 묶음 (내부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>챗봇</t>
-        </is>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>chat_messages</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="inlineStr"/>
-      <c r="G57" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="inlineStr">
-        <is>
-          <t>의료 기록으로 보관할 필요가 생길 때만</t>
         </is>
       </c>
     </row>
@@ -2974,24 +2974,24 @@
           <t>챗봇</t>
         </is>
       </c>
-      <c r="B58" s="33" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>role · content · created_at</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Communication.sender · payload.contentString · sent</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr"/>
@@ -3000,83 +3000,83 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H58" s="15" t="inlineStr"/>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>의료 기록으로 보관할 필요가 생길 때만</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
+          <t>챗봇</t>
+        </is>
+      </c>
+      <c r="B59" s="33" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>role · content · created_at</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>Communication.sender · payload.contentString · sent</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="inlineStr"/>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B59" s="19" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>recommendations</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="C60" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>CarePlan</t>
         </is>
       </c>
-      <c r="E59" s="15" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr">
         <is>
           <t>CarePlan.activity</t>
         </is>
       </c>
-      <c r="F59" s="15" t="inlineStr">
+      <c r="F60" s="15" t="inlineStr">
         <is>
           <t>추천 1개 = activity 1개 (status = not-started)</t>
         </is>
       </c>
-      <c r="G59" s="16" t="inlineStr">
+      <c r="G60" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H59" s="15" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="30" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B60" s="38" t="inlineStr">
-        <is>
-          <t>habit_goals</t>
-        </is>
-      </c>
-      <c r="C60" s="32" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D60" s="39" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="E60" s="32" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="F60" s="32" t="inlineStr"/>
-      <c r="G60" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H60" s="32" t="inlineStr">
-        <is>
-          <t>FHIR Goal = 환자 건강 목표</t>
-        </is>
-      </c>
+      <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="30" t="inlineStr">
@@ -3084,24 +3084,24 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B61" s="31" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
         <is>
           <t>habit_goals</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
         <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D61" s="32" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D61" s="39" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>Goal.description.text</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="F61" s="32" t="inlineStr"/>
@@ -3110,7 +3110,11 @@
           <t>일치</t>
         </is>
       </c>
-      <c r="H61" s="32" t="inlineStr"/>
+      <c r="H61" s="32" t="inlineStr">
+        <is>
+          <t>FHIR Goal = 환자 건강 목표</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="30" t="inlineStr">
@@ -3125,7 +3129,7 @@
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>target_value · unit</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D62" s="32" t="inlineStr">
@@ -3135,7 +3139,7 @@
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>Goal.target.detailQuantity</t>
+          <t>Goal.description.text</t>
         </is>
       </c>
       <c r="F62" s="32" t="inlineStr"/>
@@ -3159,7 +3163,7 @@
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>start_date · end_date</t>
+          <t>target_value · unit</t>
         </is>
       </c>
       <c r="D63" s="32" t="inlineStr">
@@ -3169,7 +3173,7 @@
       </c>
       <c r="E63" s="32" t="inlineStr">
         <is>
-          <t>Goal.startDate · Goal.target.dueDate</t>
+          <t>Goal.target.detailQuantity</t>
         </is>
       </c>
       <c r="F63" s="32" t="inlineStr"/>
@@ -3181,42 +3185,38 @@
       <c r="H63" s="32" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B64" s="33" t="inlineStr">
+      <c r="B64" s="31" t="inlineStr">
         <is>
           <t>habit_goals</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>start_date · end_date</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>Goal.lifecycleStatus</t>
-        </is>
-      </c>
-      <c r="F64" s="15" t="inlineStr">
-        <is>
-          <t>active → active / ended → completed</t>
-        </is>
-      </c>
-      <c r="G64" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="inlineStr"/>
+      <c r="E64" s="32" t="inlineStr">
+        <is>
+          <t>Goal.startDate · Goal.target.dueDate</t>
+        </is>
+      </c>
+      <c r="F64" s="32" t="inlineStr"/>
+      <c r="G64" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H64" s="32" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -3224,29 +3224,29 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B65" s="19" t="inlineStr">
-        <is>
-          <t>habit_records</t>
+      <c r="B65" s="33" t="inlineStr">
+        <is>
+          <t>habit_goals</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D65" s="14" t="inlineStr">
-        <is>
-          <t>Observation</t>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>Goal</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Goal.lifecycleStatus</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
+          <t>active → active / ended → completed</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr">
@@ -3262,105 +3262,109 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B66" s="33" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>habit_records</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>실천·보상</t>
+        </is>
+      </c>
+      <c r="B67" s="33" t="inlineStr">
+        <is>
+          <t>habit_records</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
           <t>value · completed · record_date</t>
         </is>
       </c>
-      <c r="D66" s="15" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="E66" s="15" t="inlineStr">
+      <c r="E67" s="15" t="inlineStr">
         <is>
           <t>Observation.valueQuantity / valueBoolean · effectiveDateTime</t>
         </is>
       </c>
-      <c r="F66" s="15" t="inlineStr"/>
-      <c r="G66" s="16" t="inlineStr">
+      <c r="F67" s="15" t="inlineStr"/>
+      <c r="G67" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H66" s="15" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="34" t="inlineStr">
+      <c r="H67" s="15" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="34" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B67" s="40" t="inlineStr">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="C67" s="36" t="inlineStr">
+      <c r="C68" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E67" s="36" t="inlineStr">
+      <c r="E68" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F67" s="36" t="inlineStr"/>
-      <c r="G67" s="34" t="inlineStr">
+      <c r="F68" s="36" t="inlineStr"/>
+      <c r="G68" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H67" s="36" t="inlineStr">
+      <c r="H68" s="36" t="inlineStr">
         <is>
           <t>포인트 (서비스 보상)</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>drug_products</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="F68" s="15" t="inlineStr"/>
-      <c r="G68" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
@@ -3368,31 +3372,27 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B69" s="33" t="inlineStr">
+      <c r="B69" s="19" t="inlineStr">
         <is>
           <t>drug_products</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>edi_code</t>
-        </is>
-      </c>
-      <c r="D69" s="15" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
         <is>
           <t>Medication</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>Medication.code.coding</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr">
-        <is>
-          <t>system = 심평원 EDI 제품코드</t>
-        </is>
-      </c>
+          <t>Medication</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="inlineStr"/>
       <c r="G69" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>ingr_code</t>
+          <t>edi_code</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Medication.ingredient.itemCodeableConcept</t>
+          <t>Medication.code.coding</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>system = 심평원 주성분코드</t>
+          <t>system = 심평원 EDI 제품코드</t>
         </is>
       </c>
       <c r="G70" s="16" t="inlineStr">
@@ -3451,20 +3451,24 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>entp_name</t>
+          <t>ingr_code</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Medication.manufacturer → Organization.name</t>
-        </is>
-      </c>
-      <c r="F71" s="15" t="inlineStr"/>
+          <t>Medication.ingredient.itemCodeableConcept</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>system = 심평원 주성분코드</t>
+        </is>
+      </c>
       <c r="G71" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3485,17 +3489,17 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>spec_value · spec_unit</t>
+          <t>entp_name</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>Medication</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Medication.ingredient.strength</t>
+          <t>Medication.manufacturer → Organization.name</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr"/>
@@ -3512,24 +3516,24 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B73" s="19" t="inlineStr">
-        <is>
-          <t>drug_ingredients</t>
+      <c r="B73" s="33" t="inlineStr">
+        <is>
+          <t>drug_products</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>Substance</t>
+          <t>spec_value · spec_unit</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>Substance.code</t>
+          <t>Medication.ingredient.strength</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr"/>
@@ -3548,7 +3552,7 @@
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>drug_details</t>
+          <t>drug_ingredients</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
@@ -3558,29 +3562,21 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>MedicationKnowledge</t>
+          <t>Substance</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>MedicationKnowledge</t>
-        </is>
-      </c>
-      <c r="F74" s="15" t="inlineStr">
-        <is>
-          <t>효능효과 · 용법용량 · 주의사항</t>
-        </is>
-      </c>
+          <t>Substance.code</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr"/>
       <c r="G74" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H74" s="15" t="inlineStr">
-        <is>
-          <t>RAG 검색 원문</t>
-        </is>
-      </c>
+      <c r="H74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -3590,7 +3586,7 @@
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>dur_interaction · dur_interaction_exception</t>
+          <t>drug_details</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
@@ -3600,17 +3596,17 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition (R5)</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.interaction</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>type = interaction</t>
+          <t>효능효과 · 용법용량 · 주의사항</t>
         </is>
       </c>
       <c r="G75" s="16" t="inlineStr">
@@ -3620,7 +3616,7 @@
       </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>R4에는 전용 리소스 없음 — R5 참고</t>
+          <t>RAG 검색 원문</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3628,7 @@
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
+          <t>dur_interaction · dur_interaction_exception</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
@@ -3647,12 +3643,12 @@
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.contraindication</t>
+          <t>ClinicalUseDefinition.interaction</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>type = contraindication, population = 나이 · 임부</t>
+          <t>type = interaction</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
@@ -3662,7 +3658,7 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>R5 참고</t>
+          <t>R4에는 전용 리소스 없음 — R5 참고</t>
         </is>
       </c>
     </row>
@@ -3674,111 +3670,115 @@
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
+          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>ClinicalUseDefinition (R5)</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>ClinicalUseDefinition.contraindication</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>type = contraindication, population = 나이 · 임부</t>
+        </is>
+      </c>
+      <c r="G77" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>R5 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
           <t>dur_dose_limit</t>
         </is>
       </c>
-      <c r="C77" s="15" t="inlineStr">
+      <c r="C78" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D77" s="14" t="inlineStr">
+      <c r="D78" s="14" t="inlineStr">
         <is>
           <t>MedicationKnowledge</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr">
         <is>
           <t>MedicationKnowledge.administrationGuidelines.dosage</t>
         </is>
       </c>
-      <c r="F77" s="15" t="inlineStr">
+      <c r="F78" s="15" t="inlineStr">
         <is>
           <t>1일 최대 투여량</t>
         </is>
       </c>
-      <c r="G77" s="16" t="inlineStr">
+      <c r="G78" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H77" s="15" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="34" t="inlineStr">
+      <c r="H78" s="15" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="34" t="inlineStr">
         <is>
           <t>마스터</t>
         </is>
       </c>
-      <c r="B78" s="40" t="inlineStr">
+      <c r="B79" s="40" t="inlineStr">
         <is>
           <t>dup_ingredient · dup_efficacy</t>
         </is>
       </c>
-      <c r="C78" s="36" t="inlineStr">
+      <c r="C79" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D78" s="17" t="inlineStr">
+      <c r="D79" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E78" s="36" t="inlineStr">
+      <c r="E79" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F78" s="36" t="inlineStr"/>
-      <c r="G78" s="34" t="inlineStr">
+      <c r="F79" s="36" t="inlineStr"/>
+      <c r="G79" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H78" s="36" t="inlineStr">
+      <c r="H79" s="36" t="inlineStr">
         <is>
           <t>국내 DUR 중복 점검 규칙</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B79" s="19" t="inlineStr">
-        <is>
-          <t>diseases</t>
-        </is>
-      </c>
-      <c r="C79" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>CodeSystem</t>
-        </is>
-      </c>
-      <c r="E79" s="15" t="inlineStr">
-        <is>
-          <t>CodeSystem.concept</t>
-        </is>
-      </c>
-      <c r="F79" s="15" t="inlineStr">
-        <is>
-          <t>KCD 상병 코드 목록</t>
-        </is>
-      </c>
-      <c r="G79" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H79" s="15" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>checkup_items</t>
+          <t>diseases</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>건강검진 검사항목 코드 목록</t>
+          <t>KCD 상병 코드 목록</t>
         </is>
       </c>
       <c r="G80" s="16" t="inlineStr">
@@ -3816,11 +3816,7 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H80" s="15" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
+      <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -3830,7 +3826,7 @@
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
+          <t>checkup_items</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
@@ -3840,15 +3836,19 @@
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>PlanDefinition</t>
+          <t>CodeSystem</t>
         </is>
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>PlanDefinition.action</t>
-        </is>
-      </c>
-      <c r="F81" s="15" t="inlineStr"/>
+          <t>CodeSystem.concept</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>건강검진 검사항목 코드 목록</t>
+        </is>
+      </c>
       <c r="G81" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="H81" s="15" t="inlineStr">
         <is>
-          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
+          <t>보류</t>
         </is>
       </c>
     </row>
@@ -3868,80 +3868,118 @@
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
+          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>PlanDefinition</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>PlanDefinition.action</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr"/>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
           <t>lifestyle_guide_sources</t>
         </is>
       </c>
-      <c r="C82" s="15" t="inlineStr">
+      <c r="C83" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D82" s="14" t="inlineStr">
+      <c r="D83" s="14" t="inlineStr">
         <is>
           <t>DocumentReference / Citation (R5)</t>
         </is>
       </c>
-      <c r="E82" s="15" t="inlineStr">
+      <c r="E83" s="15" t="inlineStr">
         <is>
           <t>PlanDefinition.relatedArtifact</t>
         </is>
       </c>
-      <c r="F82" s="15" t="inlineStr">
+      <c r="F83" s="15" t="inlineStr">
         <is>
           <t>type = citation · display = 문서명 · url · citation = 기관 · 발행일</t>
         </is>
       </c>
-      <c r="G82" s="16" t="inlineStr">
+      <c r="G83" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H82" s="15" t="inlineStr">
+      <c r="H83" s="15" t="inlineStr">
         <is>
           <t>v1.2 · R4는 relatedArtifact로 출처 표시</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="22" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
         <is>
           <t>마스터</t>
         </is>
       </c>
-      <c r="B83" s="37" t="inlineStr">
+      <c r="B84" s="37" t="inlineStr">
         <is>
           <t>lifestyle_medication_links</t>
         </is>
       </c>
-      <c r="C83" s="21" t="inlineStr">
+      <c r="C84" s="21" t="inlineStr">
         <is>
           <t>requires_clinician · goal_eligible</t>
         </is>
       </c>
-      <c r="D83" s="21" t="inlineStr">
+      <c r="D84" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E83" s="21" t="inlineStr">
+      <c r="E84" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F83" s="21" t="inlineStr"/>
-      <c r="G83" s="22" t="inlineStr">
+      <c r="F84" s="21" t="inlineStr"/>
+      <c r="G84" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H83" s="21" t="inlineStr">
+      <c r="H84" s="21" t="inlineStr">
         <is>
           <t>v1.2 · 서비스 표시 규칙</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H83"/>
+  <autoFilter ref="A5:H84"/>
   <dataValidations count="1">
     <dataValidation sqref="G6:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"일치,변환,확장,FHIR 외"</formula1>
@@ -3957,7 +3995,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6914,6 +6952,44 @@
         </is>
       </c>
       <c r="E153" s="10" t="n"/>
+    </row>
+    <row r="154" hidden="1" outlineLevel="1">
+      <c r="A154" s="10" t="n"/>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>입력 / prescription_items.guidance — 필드 추가</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>guidance jsonb · N · 약봉투 약 카드에 약국이 인쇄한 복약 안내 문장 목록 (마스킹 후 저장, 없으면 null)</t>
+        </is>
+      </c>
+      <c r="E154" s="10" t="n"/>
+    </row>
+    <row r="155" hidden="1" outlineLevel="1">
+      <c r="A155" s="10" t="n"/>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>FHIR 대응 탭 — prescription_items.guidance 행 추가</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>78행</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>79행 — guidance → MedicationRequest.dosageInstruction.patientInstruction (변환: 문장 목록 → 줄바꿈으로 이어 붙인 text)</t>
+        </is>
+      </c>
+      <c r="E155" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -8284,7 +8360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10278,68 +10354,60 @@
       <c r="N37" s="21" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>prescription_item_candidates</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>약품 매칭 후보</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F38" s="25" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="n"/>
-      <c r="H38" s="25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I38" s="24" t="n"/>
-      <c r="J38" s="24" t="inlineStr">
-        <is>
-          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
-        </is>
-      </c>
-      <c r="K38" s="24" t="inlineStr">
-        <is>
-          <t>OC-02 · O-3</t>
-        </is>
-      </c>
-      <c r="L38" s="25" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>처방 약품</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>guidance</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>약국 인쇄 복약 안내</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="21" t="n"/>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="n"/>
+      <c r="J38" s="21" t="inlineStr">
+        <is>
+          <t>약봉투만 채움, 마스킹 후 저장. 없으면 null</t>
+        </is>
+      </c>
+      <c r="K38" s="21" t="inlineStr">
+        <is>
+          <t>OC-02 · O-2 · O-3</t>
+        </is>
+      </c>
+      <c r="L38" s="22" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M38" s="25" t="inlineStr">
+      <c r="M38" s="22" t="inlineStr">
         <is>
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N38" s="24" t="inlineStr">
-        <is>
-          <t>v1.0 신규 🟡 채연 확인 · OC-02 후보 목록. 매칭 정확도(1순위 적중률 · 5순위 내 포함률) 측정에 필요 · v1.3 id PK + (item_id, rank) UQ · v1.3 edi_code · item_seq 중 하나는 꼭 있음</t>
-        </is>
-      </c>
+      <c r="N38" s="21" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
@@ -10354,12 +10422,12 @@
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>처방 약품 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -10369,21 +10437,21 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>prescription_items.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="n"/>
       <c r="H39" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="I39" s="24" t="n"/>
-      <c r="J39" s="24" t="n"/>
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
+        </is>
+      </c>
       <c r="K39" s="24" t="inlineStr">
         <is>
           <t>OC-02 · O-3</t>
@@ -10399,7 +10467,11 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N39" s="24" t="n"/>
+      <c r="N39" s="24" t="inlineStr">
+        <is>
+          <t>v1.0 신규 🟡 채연 확인 · OC-02 후보 목록. 매칭 정확도(1순위 적중률 · 5순위 내 포함률) 측정에 필요 · v1.3 id PK + (item_id, rank) UQ · v1.3 edi_code · item_seq 중 하나는 꼭 있음</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="23" t="inlineStr">
@@ -10414,32 +10486,36 @@
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>순위</t>
+          <t>처방 약품 ID</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
         <is>
-          <t>smallint</t>
-        </is>
-      </c>
-      <c r="F40" s="25" t="n"/>
-      <c r="G40" s="24" t="n"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F40" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>prescription_items.id</t>
+        </is>
+      </c>
       <c r="H40" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="I40" s="24" t="n"/>
-      <c r="J40" s="24" t="inlineStr">
-        <is>
-          <t>(item_id, rank) UQ</t>
-        </is>
-      </c>
+      <c r="J40" s="24" t="n"/>
       <c r="K40" s="24" t="inlineStr">
         <is>
           <t>OC-02 · O-3</t>
@@ -10470,38 +10546,30 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>edi_code</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>EDI 제품코드</t>
+          <t>순위</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>varchar(9)</t>
-        </is>
-      </c>
-      <c r="F41" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>drug_products.edi_code</t>
-        </is>
-      </c>
+          <t>smallint</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="n"/>
+      <c r="G41" s="24" t="n"/>
       <c r="H41" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I41" s="24" t="n"/>
       <c r="J41" s="24" t="inlineStr">
         <is>
-          <t>급여목록에 있는 약 (없는 약은 item_seq) — 둘 중 하나는 꼭 있음</t>
+          <t>(item_id, rank) UQ</t>
         </is>
       </c>
       <c r="K41" s="24" t="inlineStr">
@@ -10534,12 +10602,12 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>item_seq</t>
+          <t>edi_code</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>품목기준코드</t>
+          <t>EDI 제품코드</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -10554,7 +10622,7 @@
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>drug_details.item_seq</t>
+          <t>drug_products.edi_code</t>
         </is>
       </c>
       <c r="H42" s="25" t="inlineStr">
@@ -10565,7 +10633,7 @@
       <c r="I42" s="24" t="n"/>
       <c r="J42" s="24" t="inlineStr">
         <is>
-          <t>급여목록에 없는 약 — edi_code가 없을 때 채움</t>
+          <t>급여목록에 있는 약 (없는 약은 item_seq) — 둘 중 하나는 꼭 있음</t>
         </is>
       </c>
       <c r="K42" s="24" t="inlineStr">
@@ -10598,104 +10666,108 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
+          <t>item_seq</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>품목기준코드</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>drug_details.item_seq</t>
+        </is>
+      </c>
+      <c r="H43" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="n"/>
+      <c r="J43" s="24" t="inlineStr">
+        <is>
+          <t>급여목록에 없는 약 — edi_code가 없을 때 채움</t>
+        </is>
+      </c>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>OC-02 · O-3</t>
+        </is>
+      </c>
+      <c r="L43" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M43" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N43" s="24" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>prescription_item_candidates</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>약품 매칭 후보</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
           <t>score</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="D44" s="24" t="inlineStr">
         <is>
           <t>매칭 점수</t>
         </is>
       </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>decimal(5,4)</t>
         </is>
       </c>
-      <c r="F43" s="25" t="n"/>
-      <c r="G43" s="24" t="n"/>
-      <c r="H43" s="25" t="inlineStr">
+      <c r="F44" s="25" t="n"/>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I43" s="24" t="n"/>
-      <c r="J43" s="24" t="n"/>
-      <c r="K43" s="24" t="inlineStr">
+      <c r="I44" s="24" t="n"/>
+      <c r="J44" s="24" t="n"/>
+      <c r="K44" s="24" t="inlineStr">
         <is>
           <t>OC-02 · O-3</t>
         </is>
       </c>
-      <c r="L43" s="25" t="inlineStr">
+      <c r="L44" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M43" s="25" t="inlineStr">
+      <c r="M44" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N43" s="24" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>health_checkups</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>건강검진 (보류)</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G44" s="15" t="n"/>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="15" t="n"/>
-      <c r="K44" s="15" t="inlineStr">
-        <is>
-          <t>REQ-015</t>
-        </is>
-      </c>
-      <c r="L44" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M44" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N44" s="15" t="inlineStr">
-        <is>
-          <t>보류 (REQ-015 · 멘토링 확인 후 결정)</t>
-        </is>
-      </c>
+      <c r="N44" s="24" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
@@ -10710,12 +10782,12 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>사용자 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
@@ -10725,14 +10797,10 @@
       </c>
       <c r="F45" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="n"/>
       <c r="H45" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10755,7 +10823,11 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N45" s="15" t="n"/>
+      <c r="N45" s="15" t="inlineStr">
+        <is>
+          <t>보류 (REQ-015 · 멘토링 확인 후 결정)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
@@ -10770,24 +10842,32 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>checkup_date</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>검진일</t>
+          <t>사용자 ID</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="n"/>
-      <c r="G46" s="15" t="n"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
       <c r="H46" s="16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I46" s="15" t="n"/>
@@ -10822,17 +10902,17 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>ocr_raw_text</t>
+          <t>checkup_date</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>OCR 원문</t>
+          <t>검진일</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F47" s="16" t="n"/>
@@ -10874,17 +10954,17 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>ocr_raw_text</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>OCR 원문</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F48" s="16" t="n"/>
@@ -10894,11 +10974,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I48" s="15" t="n"/>
       <c r="J48" s="15" t="n"/>
       <c r="K48" s="15" t="inlineStr">
         <is>
@@ -10920,41 +10996,41 @@
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>checkup_results</t>
+          <t>health_checkups</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>건강검진 결과 (보류)</t>
+          <t>건강검진 (보류)</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="n"/>
       <c r="G49" s="15" t="n"/>
       <c r="H49" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="n"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J49" s="15" t="n"/>
       <c r="K49" s="15" t="inlineStr">
         <is>
@@ -10971,11 +11047,7 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N49" s="15" t="inlineStr">
-        <is>
-          <t>보류 (REQ-015)</t>
-        </is>
-      </c>
+      <c r="N49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
@@ -10990,12 +11062,12 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>checkup_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>건강검진 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
@@ -11005,14 +11077,10 @@
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G50" s="15" t="inlineStr">
-        <is>
-          <t>health_checkups.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="n"/>
       <c r="H50" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11035,67 +11103,71 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N50" s="15" t="n"/>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>보류 (REQ-015)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>checkup_results</t>
         </is>
       </c>
-      <c r="B51" s="21" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>건강검진 결과 (보류)</t>
         </is>
       </c>
-      <c r="C51" s="21" t="inlineStr">
-        <is>
-          <t>item_code</t>
-        </is>
-      </c>
-      <c r="D51" s="21" t="inlineStr">
-        <is>
-          <t>검사 항목 코드</t>
-        </is>
-      </c>
-      <c r="E51" s="21" t="inlineStr">
-        <is>
-          <t>varchar(8)</t>
-        </is>
-      </c>
-      <c r="F51" s="22" t="inlineStr">
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>checkup_id</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>건강검진 ID</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G51" s="21" t="inlineStr">
-        <is>
-          <t>checkup_items.code</t>
-        </is>
-      </c>
-      <c r="H51" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I51" s="21" t="n"/>
-      <c r="J51" s="21" t="n"/>
-      <c r="K51" s="21" t="inlineStr">
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>health_checkups.id</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="n"/>
+      <c r="J51" s="15" t="n"/>
+      <c r="K51" s="15" t="inlineStr">
         <is>
           <t>REQ-015</t>
         </is>
       </c>
-      <c r="L51" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M51" s="22" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N51" s="21" t="n"/>
+      <c r="L51" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
@@ -11110,21 +11182,29 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>value_num</t>
+          <t>item_code</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
         <is>
-          <t>결과 수치</t>
+          <t>검사 항목 코드</t>
         </is>
       </c>
       <c r="E52" s="21" t="inlineStr">
         <is>
-          <t>decimal(12,3)</t>
-        </is>
-      </c>
-      <c r="F52" s="22" t="n"/>
-      <c r="G52" s="21" t="n"/>
+          <t>varchar(8)</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>checkup_items.code</t>
+        </is>
+      </c>
       <c r="H52" s="22" t="inlineStr">
         <is>
           <t>N</t>
@@ -11162,17 +11242,17 @@
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>value_text</t>
+          <t>value_num</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>결과 판정</t>
+          <t>결과 수치</t>
         </is>
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
+          <t>decimal(12,3)</t>
         </is>
       </c>
       <c r="F53" s="22" t="n"/>
@@ -11201,8 +11281,60 @@
       </c>
       <c r="N53" s="21" t="n"/>
     </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>checkup_results</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>건강검진 결과 (보류)</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>value_text</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>결과 판정</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I54" s="21" t="n"/>
+      <c r="J54" s="21" t="n"/>
+      <c r="K54" s="21" t="inlineStr">
+        <is>
+          <t>REQ-015</t>
+        </is>
+      </c>
+      <c r="L54" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M54" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N54" s="21" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:N51"/>
+  <autoFilter ref="A4:N52"/>
   <dataValidations count="3">
     <dataValidation sqref="H5:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>

--- a/docs/planning/ERD_6기_5팀_v1.3.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.3.xlsx
@@ -20,12 +20,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'사용자'!$A$4:$N$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'입력'!$A$4:$N$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'입력'!$A$4:$N$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'분석'!$A$4:$N$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'챗봇'!$A$4:$N$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'실천·보상'!$A$4:$N$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'마스터'!$A$4:$N$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FHIR 대응'!$A$5:$H$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FHIR 대응'!$A$5:$H$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -910,6 +910,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -1680,7 +1681,11 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H24" s="15" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>10/15부터 원문을 저장하지 않아 비어 있음</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
@@ -1721,44 +1726,40 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>ocr_jobs</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>v1.2 · OCR 비동기 작업</t>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>notices</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>OCR 읽기 확인 표시는 내부 처리 정보</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1771,7 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>prescription_diseases</t>
+          <t>ocr_jobs</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -1780,17 +1781,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>처방전 질병분류기호 1개 = Condition 1개</t>
+          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
@@ -1800,7 +1801,7 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.reasonReference로 연결</t>
+          <t>v1.2 · OCR 비동기 작업</t>
         </is>
       </c>
     </row>
@@ -1810,29 +1811,29 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>prescription_diseases</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>disease_code</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Condition.code.coding</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>system = KCD (코드 시스템 URI 팀 정의 필요)</t>
+          <t>처방전 질병분류기호 1개 = Condition 1개</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
@@ -1842,7 +1843,7 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>KCD는 ICD-10 기반이라 ICD-10 코드 병기 가능</t>
+          <t>MedicationRequest.reasonReference로 연결</t>
         </is>
       </c>
     </row>
@@ -1859,152 +1860,152 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
+          <t>disease_code</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Condition.code.coding</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>system = KCD (코드 시스템 URI 팀 정의 필요)</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>KCD는 ICD-10 기반이라 ICD-10 코드 병기 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>prescription_diseases</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
           <t>is_main</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>Encounter</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Encounter.diagnosis.rank</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>주상병 → rank 1</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H29" s="15" t="inlineStr">
+      <c r="H30" s="15" t="inlineStr">
         <is>
           <t>진료(Encounter) 정보가 없으면 extension</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D30" s="39" t="inlineStr">
+      <c r="D31" s="39" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E30" s="32" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="F30" s="32" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>약 1줄 = MedicationRequest 1개</t>
         </is>
       </c>
-      <c r="G30" s="30" t="inlineStr">
+      <c r="G31" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H30" s="32" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="H31" s="32" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>edi_code</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest.medicationCodeableConcept.coding</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>system = 심평원 EDI 제품코드</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H31" s="15" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="inlineStr">
-        <is>
-          <t>raw_name</t>
-        </is>
-      </c>
-      <c r="D32" s="32" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E32" s="32" t="inlineStr">
-        <is>
-          <t>MedicationRequest.medicationCodeableConcept.text</t>
-        </is>
-      </c>
-      <c r="F32" s="32" t="inlineStr">
-        <is>
-          <t>OCR이 읽은 원문 약품명</t>
-        </is>
-      </c>
-      <c r="G32" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H32" s="32" t="inlineStr">
-        <is>
-          <t>매칭 실패해도 text는 남음</t>
-        </is>
-      </c>
+      <c r="H32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="30" t="inlineStr">
@@ -2019,64 +2020,68 @@
       </c>
       <c r="C33" s="32" t="inlineStr">
         <is>
+          <t>raw_name</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>MedicationRequest.medicationCodeableConcept.text</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>OCR이 읽은 원문 약품명</t>
+        </is>
+      </c>
+      <c r="G33" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H33" s="32" t="inlineStr">
+        <is>
+          <t>매칭 실패해도 text는 남음</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
           <t>dose_per_time</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest.dosageInstruction.doseAndRate.doseQuantity</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr"/>
-      <c r="G33" s="30" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr"/>
+      <c r="G34" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H33" s="32" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>times_per_day</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest.dosageInstruction.timing.repeat.frequency</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>period = 1, periodUnit = d</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="inlineStr"/>
+      <c r="H34" s="32" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -2091,7 +2096,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>total_days</t>
+          <t>times_per_day</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -2101,12 +2106,12 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
+          <t>MedicationRequest.dosageInstruction.timing.repeat.frequency</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>단위 d(일)</t>
+          <t>period = 1, periodUnit = d</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
@@ -2129,7 +2134,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>total_days</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
@@ -2139,12 +2144,12 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.dosageInstruction.timing.repeat.when</t>
+          <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>아침 식후 → PCM, 저녁 식후 → PCV, 취침 전 → HS 등 + text 원문</t>
+          <t>단위 d(일)</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
@@ -2167,158 +2172,154 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.dosageInstruction.timing.repeat.when</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>아침 식후 → PCM, 저녁 식후 → PCV, 취침 전 → HS 등 + text 원문</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest.dosageInstruction.patientInstruction</t>
         </is>
       </c>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>문장 목록 → 줄바꿈으로 이어 붙인 text</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="H38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>match_status · match_score</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr"/>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="F39" s="21" t="inlineStr"/>
+      <c r="G39" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
         <is>
           <t>약품 매칭 상태는 내부 처리 정보</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="34" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B39" s="40" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>prescription_item_candidates</t>
         </is>
       </c>
-      <c r="C39" s="36" t="inlineStr">
+      <c r="C40" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="36" t="inlineStr">
+      <c r="E40" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F39" s="36" t="inlineStr"/>
-      <c r="G39" s="34" t="inlineStr">
+      <c r="F40" s="36" t="inlineStr"/>
+      <c r="G40" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H39" s="36" t="inlineStr">
+      <c r="H40" s="36" t="inlineStr">
         <is>
           <t>약품 매칭 후보 (내부 처리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>health_checkups · checkup_results</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>DiagnosticReport · Observation</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>Observation.code / valueQuantity</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>검진 항목 코드 → Observation.code</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="inlineStr">
-        <is>
-          <t>보류 (REQ-015)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>analyses</t>
+          <t>health_checkups · checkup_results</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -2328,17 +2329,17 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>DiagnosticReport · Observation</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Observation.code / valueQuantity</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>분석 작업 1건 = Task 1개</t>
+          <t>검진 항목 코드 → Observation.code</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">
@@ -2348,7 +2349,7 @@
       </c>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>비동기 작업 상태를 Task로 표현</t>
+          <t>보류 (REQ-015)</t>
         </is>
       </c>
     </row>
@@ -2358,149 +2359,149 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B42" s="33" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>분석 작업 1건 = Task 1개</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>비동기 작업 상태를 Task로 표현</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>Task.status</t>
         </is>
       </c>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="F43" s="15" t="inlineStr">
         <is>
           <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H42" s="15" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>current_step · failed_step · retry_count · error_code</t>
         </is>
       </c>
-      <c r="D43" s="21" t="inlineStr">
+      <c r="D44" s="21" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E43" s="21" t="inlineStr">
+      <c r="E44" s="21" t="inlineStr">
         <is>
           <t>Task.businessStatus · Task.statusReason</t>
         </is>
       </c>
-      <c r="F43" s="21" t="inlineStr"/>
-      <c r="G43" s="22" t="inlineStr">
+      <c r="F44" s="21" t="inlineStr"/>
+      <c r="G44" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H43" s="21" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="H44" s="21" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B44" s="35" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
-      <c r="C44" s="36" t="inlineStr">
+      <c r="C45" s="36" t="inlineStr">
         <is>
           <t>user_birth_year</t>
         </is>
       </c>
-      <c r="D44" s="36" t="inlineStr">
+      <c r="D45" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E44" s="36" t="inlineStr">
+      <c r="E45" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F44" s="36" t="inlineStr"/>
-      <c r="G44" s="34" t="inlineStr">
+      <c r="F45" s="36" t="inlineStr"/>
+      <c r="G45" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H44" s="36" t="inlineStr">
+      <c r="H45" s="36" t="inlineStr">
         <is>
           <t>분석 시점 스냅샷 (내부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t>analysis_prescriptions</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>Task.input</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr">
-        <is>
-          <t>valueReference = MedicationRequest</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="inlineStr">
-        <is>
-          <t>분석에 넣은 처방 목록</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2513,7 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>analysis_diseases</t>
+          <t>analysis_prescriptions</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -2522,21 +2523,29 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr"/>
+          <t>Task.input</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>valueReference = MedicationRequest</t>
+        </is>
+      </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H46" s="15" t="inlineStr"/>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>분석에 넣은 처방 목록</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -2544,123 +2553,115 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B47" s="33" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>analysis_diseases</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr"/>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>analysis_diseases</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
           <t>origin</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>Condition.asserter</t>
         </is>
       </c>
-      <c r="F47" s="15" t="inlineStr">
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>prescription → 처방전에서 옴 / user → asserter = Patient (직접 선택)</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="G48" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H47" s="15" t="inlineStr">
+      <c r="H48" s="15" t="inlineStr">
         <is>
           <t>누가 주장한 질환인지 구분</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="30" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B48" s="38" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C48" s="32" t="inlineStr">
+      <c r="C49" s="32" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D48" s="39" t="inlineStr">
+      <c r="D49" s="39" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E48" s="32" t="inlineStr">
+      <c r="E49" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="F48" s="32" t="inlineStr">
+      <c r="F49" s="32" t="inlineStr">
         <is>
           <t>경고 1건 = DetectedIssue 1개</t>
         </is>
       </c>
-      <c r="G48" s="30" t="inlineStr">
+      <c r="G49" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H48" s="32" t="inlineStr">
+      <c r="H49" s="32" t="inlineStr">
         <is>
           <t>FHIR에 "약물 문제 감지" 전용 리소스가 있음 — 가장 잘 맞는 부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B49" s="33" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>warning_type</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue.code</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
         </is>
       </c>
     </row>
@@ -2677,68 +2678,72 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
+          <t>warning_type</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue.code</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue.severity</t>
         </is>
       </c>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>danger → high / caution → moderate / info → low</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G51" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="30" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>item_id_a · item_id_b</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="E51" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue.implicated</t>
-        </is>
-      </c>
-      <c r="F51" s="32" t="inlineStr">
-        <is>
-          <t>Reference(MedicationRequest) 2개</t>
-        </is>
-      </c>
-      <c r="G51" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H51" s="32" t="inlineStr"/>
+      <c r="H51" s="15" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="30" t="inlineStr">
@@ -2753,142 +2758,142 @@
       </c>
       <c r="C52" s="32" t="inlineStr">
         <is>
+          <t>item_id_a · item_id_b</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E52" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue.implicated</t>
+        </is>
+      </c>
+      <c r="F52" s="32" t="inlineStr">
+        <is>
+          <t>Reference(MedicationRequest) 2개</t>
+        </is>
+      </c>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H52" s="32" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="D52" s="32" t="inlineStr">
+      <c r="D53" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E52" s="32" t="inlineStr">
+      <c r="E53" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue.detail</t>
         </is>
       </c>
-      <c r="F52" s="32" t="inlineStr">
+      <c r="F53" s="32" t="inlineStr">
         <is>
           <t>DUR 금기 사유 원문</t>
         </is>
       </c>
-      <c r="G52" s="30" t="inlineStr">
+      <c r="G53" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H52" s="32" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="H53" s="32" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B53" s="33" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>source · notice_date</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue.reference</t>
         </is>
       </c>
-      <c r="F53" s="15" t="inlineStr">
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>식약처 고시 출처</t>
         </is>
       </c>
-      <c r="G53" s="16" t="inlineStr">
+      <c r="G54" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H53" s="15" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="H54" s="15" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B55" s="37" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C54" s="21" t="inlineStr">
+      <c r="C55" s="21" t="inlineStr">
         <is>
           <t>summary · daily_total · max_daily</t>
         </is>
       </c>
-      <c r="D54" s="21" t="inlineStr">
+      <c r="D55" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
+      <c r="E55" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F54" s="21" t="inlineStr"/>
-      <c r="G54" s="22" t="inlineStr">
+      <c r="F55" s="21" t="inlineStr"/>
+      <c r="G55" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H54" s="21" t="inlineStr">
+      <c r="H55" s="21" t="inlineStr">
         <is>
           <t>화면 문장 · 용량 계산값</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="34" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B55" s="40" t="inlineStr">
-        <is>
-          <t>guides</t>
-        </is>
-      </c>
-      <c r="C55" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="36" t="inlineStr"/>
-      <c r="G55" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H55" s="36" t="inlineStr">
-        <is>
-          <t>AI 생성 안내문 (의료 기록 아님). 필요하면 DocumentReference로 보관</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2905,7 @@
       </c>
       <c r="B56" s="40" t="inlineStr">
         <is>
-          <t>feedbacks</t>
+          <t>guides</t>
         </is>
       </c>
       <c r="C56" s="36" t="inlineStr">
@@ -2926,19 +2931,19 @@
       </c>
       <c r="H56" s="36" t="inlineStr">
         <is>
-          <t>서비스 피드백</t>
+          <t>AI 생성 안내문 (의료 기록 아님). 필요하면 DocumentReference로 보관</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>챗봇</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B57" s="40" t="inlineStr">
         <is>
-          <t>chat_sessions</t>
+          <t>feedbacks</t>
         </is>
       </c>
       <c r="C57" s="36" t="inlineStr">
@@ -2964,45 +2969,45 @@
       </c>
       <c r="H57" s="36" t="inlineStr">
         <is>
+          <t>서비스 피드백</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>챗봇</t>
+        </is>
+      </c>
+      <c r="B58" s="40" t="inlineStr">
+        <is>
+          <t>chat_sessions</t>
+        </is>
+      </c>
+      <c r="C58" s="36" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="36" t="inlineStr"/>
+      <c r="G58" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H58" s="36" t="inlineStr">
+        <is>
           <t>대화 묶음 (내부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>챗봇</t>
-        </is>
-      </c>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>chat_messages</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="F58" s="15" t="inlineStr"/>
-      <c r="G58" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H58" s="15" t="inlineStr">
-        <is>
-          <t>의료 기록으로 보관할 필요가 생길 때만</t>
         </is>
       </c>
     </row>
@@ -3012,24 +3017,24 @@
           <t>챗봇</t>
         </is>
       </c>
-      <c r="B59" s="33" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>role · content · created_at</t>
-        </is>
-      </c>
-      <c r="D59" s="15" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>Communication.sender · payload.contentString · sent</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr"/>
@@ -3038,83 +3043,83 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H59" s="15" t="inlineStr"/>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>의료 기록으로 보관할 필요가 생길 때만</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
+          <t>챗봇</t>
+        </is>
+      </c>
+      <c r="B60" s="33" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>role · content · created_at</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>Communication.sender · payload.contentString · sent</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="inlineStr"/>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B60" s="19" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>recommendations</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>CarePlan</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
         <is>
           <t>CarePlan.activity</t>
         </is>
       </c>
-      <c r="F60" s="15" t="inlineStr">
+      <c r="F61" s="15" t="inlineStr">
         <is>
           <t>추천 1개 = activity 1개 (status = not-started)</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="G61" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H60" s="15" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="30" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B61" s="38" t="inlineStr">
-        <is>
-          <t>habit_goals</t>
-        </is>
-      </c>
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D61" s="39" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="E61" s="32" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="F61" s="32" t="inlineStr"/>
-      <c r="G61" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H61" s="32" t="inlineStr">
-        <is>
-          <t>FHIR Goal = 환자 건강 목표</t>
-        </is>
-      </c>
+      <c r="H61" s="15" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="30" t="inlineStr">
@@ -3122,24 +3127,24 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B62" s="31" t="inlineStr">
+      <c r="B62" s="38" t="inlineStr">
         <is>
           <t>habit_goals</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D62" s="32" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D62" s="39" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>Goal.description.text</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="F62" s="32" t="inlineStr"/>
@@ -3148,7 +3153,11 @@
           <t>일치</t>
         </is>
       </c>
-      <c r="H62" s="32" t="inlineStr"/>
+      <c r="H62" s="32" t="inlineStr">
+        <is>
+          <t>FHIR Goal = 환자 건강 목표</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="30" t="inlineStr">
@@ -3163,7 +3172,7 @@
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>target_value · unit</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D63" s="32" t="inlineStr">
@@ -3173,7 +3182,7 @@
       </c>
       <c r="E63" s="32" t="inlineStr">
         <is>
-          <t>Goal.target.detailQuantity</t>
+          <t>Goal.description.text</t>
         </is>
       </c>
       <c r="F63" s="32" t="inlineStr"/>
@@ -3197,7 +3206,7 @@
       </c>
       <c r="C64" s="32" t="inlineStr">
         <is>
-          <t>start_date · end_date</t>
+          <t>target_value · unit</t>
         </is>
       </c>
       <c r="D64" s="32" t="inlineStr">
@@ -3207,7 +3216,7 @@
       </c>
       <c r="E64" s="32" t="inlineStr">
         <is>
-          <t>Goal.startDate · Goal.target.dueDate</t>
+          <t>Goal.target.detailQuantity</t>
         </is>
       </c>
       <c r="F64" s="32" t="inlineStr"/>
@@ -3219,42 +3228,38 @@
       <c r="H64" s="32" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="A65" s="30" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B65" s="33" t="inlineStr">
+      <c r="B65" s="31" t="inlineStr">
         <is>
           <t>habit_goals</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>start_date · end_date</t>
+        </is>
+      </c>
+      <c r="D65" s="32" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>Goal.lifecycleStatus</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>active → active / ended → completed</t>
-        </is>
-      </c>
-      <c r="G65" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="inlineStr"/>
+      <c r="E65" s="32" t="inlineStr">
+        <is>
+          <t>Goal.startDate · Goal.target.dueDate</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr"/>
+      <c r="G65" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H65" s="32" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -3262,29 +3267,29 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B66" s="19" t="inlineStr">
-        <is>
-          <t>habit_records</t>
+      <c r="B66" s="33" t="inlineStr">
+        <is>
+          <t>habit_goals</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>Observation</t>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>Goal</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Goal.lifecycleStatus</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
+          <t>active → active / ended → completed</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr">
@@ -3300,105 +3305,109 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B67" s="33" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>habit_records</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>실천·보상</t>
+        </is>
+      </c>
+      <c r="B68" s="33" t="inlineStr">
+        <is>
+          <t>habit_records</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
           <t>value · completed · record_date</t>
         </is>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="E67" s="15" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr">
         <is>
           <t>Observation.valueQuantity / valueBoolean · effectiveDateTime</t>
         </is>
       </c>
-      <c r="F67" s="15" t="inlineStr"/>
-      <c r="G67" s="16" t="inlineStr">
+      <c r="F68" s="15" t="inlineStr"/>
+      <c r="G68" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H67" s="15" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="34" t="inlineStr">
+      <c r="H68" s="15" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="34" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B68" s="40" t="inlineStr">
+      <c r="B69" s="40" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="C68" s="36" t="inlineStr">
+      <c r="C69" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E68" s="36" t="inlineStr">
+      <c r="E69" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F68" s="36" t="inlineStr"/>
-      <c r="G68" s="34" t="inlineStr">
+      <c r="F69" s="36" t="inlineStr"/>
+      <c r="G69" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H68" s="36" t="inlineStr">
+      <c r="H69" s="36" t="inlineStr">
         <is>
           <t>포인트 (서비스 보상)</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>drug_products</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr"/>
-      <c r="G69" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -3406,31 +3415,27 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B70" s="33" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>drug_products</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>edi_code</t>
-        </is>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
         <is>
           <t>Medication</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Medication.code.coding</t>
-        </is>
-      </c>
-      <c r="F70" s="15" t="inlineStr">
-        <is>
-          <t>system = 심평원 EDI 제품코드</t>
-        </is>
-      </c>
+          <t>Medication</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr"/>
       <c r="G70" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3451,7 +3456,7 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>ingr_code</t>
+          <t>edi_code</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
@@ -3461,12 +3466,12 @@
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Medication.ingredient.itemCodeableConcept</t>
+          <t>Medication.code.coding</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>system = 심평원 주성분코드</t>
+          <t>system = 심평원 EDI 제품코드</t>
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr">
@@ -3489,20 +3494,24 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>entp_name</t>
+          <t>ingr_code</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Medication.manufacturer → Organization.name</t>
-        </is>
-      </c>
-      <c r="F72" s="15" t="inlineStr"/>
+          <t>Medication.ingredient.itemCodeableConcept</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>system = 심평원 주성분코드</t>
+        </is>
+      </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3523,17 +3532,17 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>spec_value · spec_unit</t>
+          <t>entp_name</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>Medication</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>Medication.ingredient.strength</t>
+          <t>Medication.manufacturer → Organization.name</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr"/>
@@ -3550,24 +3559,24 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>drug_ingredients</t>
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t>drug_products</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D74" s="14" t="inlineStr">
-        <is>
-          <t>Substance</t>
+          <t>spec_value · spec_unit</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Substance.code</t>
+          <t>Medication.ingredient.strength</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr"/>
@@ -3586,7 +3595,7 @@
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>drug_details</t>
+          <t>drug_ingredients</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
@@ -3596,29 +3605,21 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>MedicationKnowledge</t>
+          <t>Substance</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>MedicationKnowledge</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="inlineStr">
-        <is>
-          <t>효능효과 · 용법용량 · 주의사항</t>
-        </is>
-      </c>
+          <t>Substance.code</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr"/>
       <c r="G75" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H75" s="15" t="inlineStr">
-        <is>
-          <t>RAG 검색 원문</t>
-        </is>
-      </c>
+      <c r="H75" s="15" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -3628,7 +3629,7 @@
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>dur_interaction · dur_interaction_exception</t>
+          <t>drug_details</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
@@ -3638,17 +3639,17 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition (R5)</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.interaction</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>type = interaction</t>
+          <t>효능효과 · 용법용량 · 주의사항</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
@@ -3658,7 +3659,7 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>R4에는 전용 리소스 없음 — R5 참고</t>
+          <t>RAG 검색 원문</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3671,7 @@
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
+          <t>dur_interaction · dur_interaction_exception</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
@@ -3685,12 +3686,12 @@
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.contraindication</t>
+          <t>ClinicalUseDefinition.interaction</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>type = contraindication, population = 나이 · 임부</t>
+          <t>type = interaction</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
@@ -3700,7 +3701,7 @@
       </c>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>R5 참고</t>
+          <t>R4에는 전용 리소스 없음 — R5 참고</t>
         </is>
       </c>
     </row>
@@ -3712,111 +3713,115 @@
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
+          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>ClinicalUseDefinition (R5)</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>ClinicalUseDefinition.contraindication</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>type = contraindication, population = 나이 · 임부</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>R5 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
           <t>dur_dose_limit</t>
         </is>
       </c>
-      <c r="C78" s="15" t="inlineStr">
+      <c r="C79" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr">
+      <c r="D79" s="14" t="inlineStr">
         <is>
           <t>MedicationKnowledge</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr">
+      <c r="E79" s="15" t="inlineStr">
         <is>
           <t>MedicationKnowledge.administrationGuidelines.dosage</t>
         </is>
       </c>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="F79" s="15" t="inlineStr">
         <is>
           <t>1일 최대 투여량</t>
         </is>
       </c>
-      <c r="G78" s="16" t="inlineStr">
+      <c r="G79" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H78" s="15" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="34" t="inlineStr">
+      <c r="H79" s="15" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="34" t="inlineStr">
         <is>
           <t>마스터</t>
         </is>
       </c>
-      <c r="B79" s="40" t="inlineStr">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t>dup_ingredient · dup_efficacy</t>
         </is>
       </c>
-      <c r="C79" s="36" t="inlineStr">
+      <c r="C80" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D80" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E79" s="36" t="inlineStr">
+      <c r="E80" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F79" s="36" t="inlineStr"/>
-      <c r="G79" s="34" t="inlineStr">
+      <c r="F80" s="36" t="inlineStr"/>
+      <c r="G80" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H79" s="36" t="inlineStr">
+      <c r="H80" s="36" t="inlineStr">
         <is>
           <t>국내 DUR 중복 점검 규칙</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B80" s="19" t="inlineStr">
-        <is>
-          <t>diseases</t>
-        </is>
-      </c>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="inlineStr">
-        <is>
-          <t>CodeSystem</t>
-        </is>
-      </c>
-      <c r="E80" s="15" t="inlineStr">
-        <is>
-          <t>CodeSystem.concept</t>
-        </is>
-      </c>
-      <c r="F80" s="15" t="inlineStr">
-        <is>
-          <t>KCD 상병 코드 목록</t>
-        </is>
-      </c>
-      <c r="G80" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -3826,7 +3831,7 @@
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>checkup_items</t>
+          <t>diseases</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
@@ -3846,7 +3851,7 @@
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>건강검진 검사항목 코드 목록</t>
+          <t>KCD 상병 코드 목록</t>
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr">
@@ -3854,11 +3859,7 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H81" s="15" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
+      <c r="H81" s="15" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -3868,7 +3869,7 @@
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
+          <t>checkup_items</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -3878,15 +3879,19 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>PlanDefinition</t>
+          <t>CodeSystem</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>PlanDefinition.action</t>
-        </is>
-      </c>
-      <c r="F82" s="15" t="inlineStr"/>
+          <t>CodeSystem.concept</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>건강검진 검사항목 코드 목록</t>
+        </is>
+      </c>
       <c r="G82" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3894,7 +3899,7 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
+          <t>보류</t>
         </is>
       </c>
     </row>
@@ -3906,80 +3911,118 @@
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
+          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>PlanDefinition</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>PlanDefinition.action</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr"/>
+      <c r="G83" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
           <t>lifestyle_guide_sources</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
+      <c r="C84" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
+      <c r="D84" s="14" t="inlineStr">
         <is>
           <t>DocumentReference / Citation (R5)</t>
         </is>
       </c>
-      <c r="E83" s="15" t="inlineStr">
+      <c r="E84" s="15" t="inlineStr">
         <is>
           <t>PlanDefinition.relatedArtifact</t>
         </is>
       </c>
-      <c r="F83" s="15" t="inlineStr">
+      <c r="F84" s="15" t="inlineStr">
         <is>
           <t>type = citation · display = 문서명 · url · citation = 기관 · 발행일</t>
         </is>
       </c>
-      <c r="G83" s="16" t="inlineStr">
+      <c r="G84" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H83" s="15" t="inlineStr">
+      <c r="H84" s="15" t="inlineStr">
         <is>
           <t>v1.2 · R4는 relatedArtifact로 출처 표시</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="22" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="22" t="inlineStr">
         <is>
           <t>마스터</t>
         </is>
       </c>
-      <c r="B84" s="37" t="inlineStr">
+      <c r="B85" s="37" t="inlineStr">
         <is>
           <t>lifestyle_medication_links</t>
         </is>
       </c>
-      <c r="C84" s="21" t="inlineStr">
+      <c r="C85" s="21" t="inlineStr">
         <is>
           <t>requires_clinician · goal_eligible</t>
         </is>
       </c>
-      <c r="D84" s="21" t="inlineStr">
+      <c r="D85" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E84" s="21" t="inlineStr">
+      <c r="E85" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F84" s="21" t="inlineStr"/>
-      <c r="G84" s="22" t="inlineStr">
+      <c r="F85" s="21" t="inlineStr"/>
+      <c r="G85" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H84" s="21" t="inlineStr">
+      <c r="H85" s="21" t="inlineStr">
         <is>
           <t>v1.2 · 서비스 표시 규칙</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H84"/>
+  <autoFilter ref="A5:H85"/>
   <dataValidations count="1">
     <dataValidation sqref="G6:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"일치,변환,확장,FHIR 외"</formula1>
@@ -3995,7 +4038,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6990,6 +7033,63 @@
         </is>
       </c>
       <c r="E155" s="10" t="n"/>
+    </row>
+    <row r="156" hidden="1" outlineLevel="1">
+      <c r="A156" s="10" t="n"/>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>입력 / prescriptions.ocr_raw_text / 설명</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>OCR 원문 (원본 이미지는 저장하지 않음) · 암호화</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>OCR 원문 — 저장하지 않음 (10/15 결정, 칸은 남겨 두고 비워 둠) · 원본 이미지도 저장하지 않음</t>
+        </is>
+      </c>
+      <c r="E156" s="10" t="n"/>
+    </row>
+    <row r="157" hidden="1" outlineLevel="1">
+      <c r="A157" s="10" t="n"/>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>입력 / prescriptions.notices — 필드 추가</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>notices jsonb · N · 사진을 읽을 때 사용자가 확인해야 할 점 문장 목록 (줄 수 불일치 · 칸 순서 추정 · 날짜 이상 등, 없으면 null)</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="n"/>
+    </row>
+    <row r="158" hidden="1" outlineLevel="1">
+      <c r="A158" s="10" t="n"/>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>FHIR 대응 탭 — prescriptions.notices 행 추가</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>79행</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>80행 — notices → extension (확장: OCR 읽기 확인 표시는 내부 처리 정보)</t>
+        </is>
+      </c>
+      <c r="E158" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -8360,7 +8460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8393,6 +8493,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -9301,7 +9402,7 @@
       <c r="I19" s="21" t="n"/>
       <c r="J19" s="21" t="inlineStr">
         <is>
-          <t>OCR 원문 (원본 이미지는 저장하지 않음) · 암호화</t>
+          <t>OCR 원문 — 저장하지 않음 (10/15 결정, 칸은 남겨 두고 비워 둠) · 원본 이미지도 저장하지 않음</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -9316,7 +9417,7 @@
       </c>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="N19" s="21" t="n"/>
@@ -9430,124 +9531,116 @@
       <c r="N21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>prescriptions</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>처방전 · 약봉투</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>notices</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>읽기 확인 표시</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>사진을 읽을 때 사용자가 확인해야 할 점 문장 목록 (줄 수 불일치 · 칸 순서 추정 · 날짜 이상 등). 없으면 null</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>OC-01 · OC-02 · O-1 · O-2</t>
+        </is>
+      </c>
+      <c r="L22" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M22" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N22" s="24" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>처방전 · 약봉투</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <t>OC-01 · OC-02 · O-1 · O-2</t>
         </is>
       </c>
-      <c r="L22" s="16" t="inlineStr">
+      <c r="L23" s="16" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr">
+      <c r="M23" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>prescription_diseases</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>처방전 질병코드</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F23" s="25" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="n"/>
-      <c r="H23" s="25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="n"/>
-      <c r="J23" s="24" t="inlineStr">
-        <is>
-          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
-        </is>
-      </c>
-      <c r="K23" s="24" t="inlineStr">
-        <is>
-          <t>O-2 · R-4</t>
-        </is>
-      </c>
-      <c r="L23" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M23" s="25" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N23" s="24" t="inlineStr">
-        <is>
-          <t>v1.0 신규 · 처방전 질병분류기호는 주상병 + 부상병 여러 개 · v1.3 id PK + (prescription_id, disease_id) UQ</t>
-        </is>
-      </c>
+      <c r="N23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
@@ -9562,12 +9655,12 @@
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>prescription_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>처방전 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -9577,21 +9670,21 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G24" s="24" t="inlineStr">
-        <is>
-          <t>prescriptions.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="n"/>
       <c r="H24" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="I24" s="24" t="n"/>
-      <c r="J24" s="24" t="n"/>
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
+        </is>
+      </c>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>O-2 · R-4</t>
@@ -9607,7 +9700,11 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N24" s="24" t="n"/>
+      <c r="N24" s="24" t="inlineStr">
+        <is>
+          <t>v1.0 신규 · 처방전 질병분류기호는 주상병 + 부상병 여러 개 · v1.3 id PK + (prescription_id, disease_id) UQ</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
@@ -9622,17 +9719,17 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>disease_id</t>
+          <t>prescription_id</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>상병 코드</t>
+          <t>처방전 ID</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>varchar(10)</t>
+          <t>bigint</t>
         </is>
       </c>
       <c r="F25" s="25" t="inlineStr">
@@ -9642,7 +9739,7 @@
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>diseases.code</t>
+          <t>prescriptions.id</t>
         </is>
       </c>
       <c r="H25" s="25" t="inlineStr">
@@ -9651,11 +9748,7 @@
         </is>
       </c>
       <c r="I25" s="24" t="n"/>
-      <c r="J25" s="24" t="inlineStr">
-        <is>
-          <t>값은 상병기호 (예: I10). (prescription_id, disease_id) UQ — 칸 이름은 Tortoise 규칙에 맞춤</t>
-        </is>
-      </c>
+      <c r="J25" s="24" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>O-2 · R-4</t>
@@ -9686,108 +9779,112 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>is_main</t>
+          <t>disease_id</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>주상병 여부</t>
+          <t>상병 코드</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="F26" s="25" t="n"/>
-      <c r="G26" s="24" t="n"/>
+          <t>varchar(10)</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>diseases.code</t>
+        </is>
+      </c>
       <c r="H26" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I26" s="24" t="n"/>
       <c r="J26" s="24" t="inlineStr">
         <is>
+          <t>값은 상병기호 (예: I10). (prescription_id, disease_id) UQ — 칸 이름은 Tortoise 규칙에 맞춤</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>O-2 · R-4</t>
+        </is>
+      </c>
+      <c r="L26" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M26" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>prescription_diseases</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>처방전 질병코드</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>is_main</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
           <t>주상병 여부</t>
         </is>
       </c>
-      <c r="K26" s="24" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>주상병 여부</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
         <is>
           <t>O-2 · R-4</t>
         </is>
       </c>
-      <c r="L26" s="25" t="inlineStr">
+      <c r="L27" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M26" s="25" t="inlineStr">
+      <c r="M27" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N26" s="24" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>처방 약품</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="15" t="inlineStr">
-        <is>
-          <t>OC-02 · O-2 · O-3</t>
-        </is>
-      </c>
-      <c r="L27" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N27" s="15" t="inlineStr">
-        <is>
-          <t>needs_confirm · unmatched가 남아 있으면 분석 시작 불가 (REQ-033). 1일 총량 = dose_per_time * times_per_day. 약이 정해졌으면(auto · user_confirmed) edi_code · item_seq 중 하나는 있음</t>
-        </is>
-      </c>
+      <c r="N27" s="24" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
@@ -9802,12 +9899,12 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>prescription_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>처방전 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
@@ -9817,14 +9914,10 @@
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G28" s="15" t="inlineStr">
-        <is>
-          <t>prescriptions.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="n"/>
       <c r="H28" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -9847,71 +9940,71 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N28" s="15" t="n"/>
+      <c r="N28" s="15" t="inlineStr">
+        <is>
+          <t>needs_confirm · unmatched가 남아 있으면 분석 시작 불가 (REQ-033). 1일 총량 = dose_per_time * times_per_day. 약이 정해졌으면(auto · user_confirmed) edi_code · item_seq 중 하나는 있음</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>처방 약품</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>edi_code</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>EDI 제품코드</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>varchar(9)</t>
-        </is>
-      </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>prescription_id</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>처방전 ID</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
-        <is>
-          <t>drug_products.edi_code</t>
-        </is>
-      </c>
-      <c r="H29" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="n"/>
-      <c r="J29" s="21" t="inlineStr">
-        <is>
-          <t>매칭 실패 · 제외 · 급여목록에 없는 약이면 null</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="inlineStr">
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>prescriptions.id</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="15" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
         </is>
       </c>
-      <c r="L29" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M29" s="22" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N29" s="21" t="n"/>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
@@ -9926,12 +10019,12 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>item_seq</t>
+          <t>edi_code</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>품목기준코드</t>
+          <t>EDI 제품코드</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -9946,7 +10039,7 @@
       </c>
       <c r="G30" s="21" t="inlineStr">
         <is>
-          <t>drug_details.item_seq</t>
+          <t>drug_products.edi_code</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -9957,133 +10050,145 @@
       <c r="I30" s="21" t="n"/>
       <c r="J30" s="21" t="inlineStr">
         <is>
+          <t>매칭 실패 · 제외 · 급여목록에 없는 약이면 null</t>
+        </is>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>OC-02 · O-2 · O-3</t>
+        </is>
+      </c>
+      <c r="L30" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M30" s="22" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>처방 약품</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>item_seq</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>품목기준코드</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>drug_details.item_seq</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="n"/>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
           <t>급여목록에 없는 약(일반약 등)만 채움 — 있는 약은 edi_code로 약 정보까지 이어짐</t>
         </is>
       </c>
-      <c r="K30" s="21" t="inlineStr">
+      <c r="K31" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
         </is>
       </c>
-      <c r="L30" s="22" t="inlineStr">
+      <c r="L31" s="22" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M30" s="22" t="inlineStr">
+      <c r="M31" s="22" t="inlineStr">
         <is>
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N30" s="21" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="N31" s="21" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>처방 약품</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>raw_name</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>인식된 약품명</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>varchar(300)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="16" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="inlineStr">
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="inlineStr">
         <is>
           <t>OCR이 읽은 원문 약품명</t>
         </is>
       </c>
-      <c r="K31" s="15" t="inlineStr">
+      <c r="K32" s="15" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
         </is>
       </c>
-      <c r="L31" s="16" t="inlineStr">
+      <c r="L32" s="16" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M31" s="16" t="inlineStr">
+      <c r="M32" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N31" s="15" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>처방 약품</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>match_score</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>매칭 점수</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>decimal(5,4)</t>
-        </is>
-      </c>
-      <c r="F32" s="22" t="n"/>
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="n"/>
-      <c r="J32" s="21" t="n"/>
-      <c r="K32" s="21" t="inlineStr">
-        <is>
-          <t>OC-02 · O-2 · O-3</t>
-        </is>
-      </c>
-      <c r="L32" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M32" s="22" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N32" s="21" t="n"/>
+      <c r="N32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
@@ -10098,32 +10203,28 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>match_status</t>
+          <t>match_score</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>매칭 상태</t>
+          <t>매칭 점수</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>decimal(5,4)</t>
         </is>
       </c>
       <c r="F33" s="22" t="n"/>
       <c r="G33" s="21" t="n"/>
       <c r="H33" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I33" s="21" t="n"/>
-      <c r="J33" s="21" t="inlineStr">
-        <is>
-          <t>auto / needs_confirm / user_confirmed / unmatched / excluded(빼고 진행)</t>
-        </is>
-      </c>
+      <c r="J33" s="21" t="n"/>
       <c r="K33" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
@@ -10154,28 +10255,32 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>dose_per_time</t>
+          <t>match_status</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>1회 투여량</t>
+          <t>매칭 상태</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>decimal(10,3)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="F34" s="22" t="n"/>
       <c r="G34" s="21" t="n"/>
       <c r="H34" s="22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="n"/>
+      <c r="J34" s="21" t="inlineStr">
+        <is>
+          <t>auto / needs_confirm / user_confirmed / unmatched / excluded(빼고 진행)</t>
+        </is>
+      </c>
       <c r="K34" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
@@ -10206,17 +10311,17 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>times_per_day</t>
+          <t>dose_per_time</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>1일 투여 횟수</t>
+          <t>1회 투여량</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>decimal(10,3)</t>
         </is>
       </c>
       <c r="F35" s="22" t="n"/>
@@ -10258,12 +10363,12 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>total_days</t>
+          <t>times_per_day</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>총 투약일수</t>
+          <t>1일 투여 횟수</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -10310,17 +10415,17 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>total_days</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>복용 시점</t>
+          <t>총 투약일수</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="F37" s="22" t="n"/>
@@ -10331,11 +10436,7 @@
         </is>
       </c>
       <c r="I37" s="21" t="n"/>
-      <c r="J37" s="21" t="inlineStr">
-        <is>
-          <t>아침 식후 등</t>
-        </is>
-      </c>
+      <c r="J37" s="21" t="n"/>
       <c r="K37" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
@@ -10366,17 +10467,17 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>guidance</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>약국 인쇄 복약 안내</t>
+          <t>복용 시점</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>jsonb</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F38" s="22" t="n"/>
@@ -10389,89 +10490,81 @@
       <c r="I38" s="21" t="n"/>
       <c r="J38" s="21" t="inlineStr">
         <is>
+          <t>아침 식후 등</t>
+        </is>
+      </c>
+      <c r="K38" s="21" t="inlineStr">
+        <is>
+          <t>OC-02 · O-2 · O-3</t>
+        </is>
+      </c>
+      <c r="L38" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M38" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N38" s="21" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>처방 약품</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>guidance</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>약국 인쇄 복약 안내</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="21" t="n"/>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="n"/>
+      <c r="J39" s="21" t="inlineStr">
+        <is>
           <t>약봉투만 채움, 마스킹 후 저장. 없으면 null</t>
         </is>
       </c>
-      <c r="K38" s="21" t="inlineStr">
+      <c r="K39" s="21" t="inlineStr">
         <is>
           <t>OC-02 · O-2 · O-3</t>
         </is>
       </c>
-      <c r="L38" s="22" t="inlineStr">
+      <c r="L39" s="22" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M38" s="22" t="inlineStr">
+      <c r="M39" s="22" t="inlineStr">
         <is>
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N38" s="21" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>prescription_item_candidates</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>약품 매칭 후보</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F39" s="25" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I39" s="24" t="n"/>
-      <c r="J39" s="24" t="inlineStr">
-        <is>
-          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
-        </is>
-      </c>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>OC-02 · O-3</t>
-        </is>
-      </c>
-      <c r="L39" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M39" s="25" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N39" s="24" t="inlineStr">
-        <is>
-          <t>v1.0 신규 🟡 채연 확인 · OC-02 후보 목록. 매칭 정확도(1순위 적중률 · 5순위 내 포함률) 측정에 필요 · v1.3 id PK + (item_id, rank) UQ · v1.3 edi_code · item_seq 중 하나는 꼭 있음</t>
-        </is>
-      </c>
+      <c r="N39" s="21" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="23" t="inlineStr">
@@ -10486,12 +10579,12 @@
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>처방 약품 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
@@ -10501,21 +10594,21 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="inlineStr">
-        <is>
-          <t>prescription_items.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="n"/>
       <c r="H40" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="I40" s="24" t="n"/>
-      <c r="J40" s="24" t="n"/>
+      <c r="J40" s="24" t="inlineStr">
+        <is>
+          <t>코드 구현 맞춤 — Tortoise는 복합 PK를 지원하지 않아 id를 PK로 두고 원래 PK 두 칸은 unique로</t>
+        </is>
+      </c>
       <c r="K40" s="24" t="inlineStr">
         <is>
           <t>OC-02 · O-3</t>
@@ -10531,7 +10624,11 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="N40" s="24" t="n"/>
+      <c r="N40" s="24" t="inlineStr">
+        <is>
+          <t>v1.0 신규 🟡 채연 확인 · OC-02 후보 목록. 매칭 정확도(1순위 적중률 · 5순위 내 포함률) 측정에 필요 · v1.3 id PK + (item_id, rank) UQ · v1.3 edi_code · item_seq 중 하나는 꼭 있음</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
@@ -10546,32 +10643,36 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>순위</t>
+          <t>처방 약품 ID</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>smallint</t>
-        </is>
-      </c>
-      <c r="F41" s="25" t="n"/>
-      <c r="G41" s="24" t="n"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>prescription_items.id</t>
+        </is>
+      </c>
       <c r="H41" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="I41" s="24" t="n"/>
-      <c r="J41" s="24" t="inlineStr">
-        <is>
-          <t>(item_id, rank) UQ</t>
-        </is>
-      </c>
+      <c r="J41" s="24" t="n"/>
       <c r="K41" s="24" t="inlineStr">
         <is>
           <t>OC-02 · O-3</t>
@@ -10602,38 +10703,30 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>edi_code</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>EDI 제품코드</t>
+          <t>순위</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
         <is>
-          <t>varchar(9)</t>
-        </is>
-      </c>
-      <c r="F42" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>drug_products.edi_code</t>
-        </is>
-      </c>
+          <t>smallint</t>
+        </is>
+      </c>
+      <c r="F42" s="25" t="n"/>
+      <c r="G42" s="24" t="n"/>
       <c r="H42" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I42" s="24" t="n"/>
       <c r="J42" s="24" t="inlineStr">
         <is>
-          <t>급여목록에 있는 약 (없는 약은 item_seq) — 둘 중 하나는 꼭 있음</t>
+          <t>(item_id, rank) UQ</t>
         </is>
       </c>
       <c r="K42" s="24" t="inlineStr">
@@ -10666,12 +10759,12 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>item_seq</t>
+          <t>edi_code</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>품목기준코드</t>
+          <t>EDI 제품코드</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -10686,7 +10779,7 @@
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>drug_details.item_seq</t>
+          <t>drug_products.edi_code</t>
         </is>
       </c>
       <c r="H43" s="25" t="inlineStr">
@@ -10697,7 +10790,7 @@
       <c r="I43" s="24" t="n"/>
       <c r="J43" s="24" t="inlineStr">
         <is>
-          <t>급여목록에 없는 약 — edi_code가 없을 때 채움</t>
+          <t>급여목록에 있는 약 (없는 약은 item_seq) — 둘 중 하나는 꼭 있음</t>
         </is>
       </c>
       <c r="K43" s="24" t="inlineStr">
@@ -10730,104 +10823,108 @@
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
+          <t>item_seq</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>품목기준코드</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F44" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>drug_details.item_seq</t>
+        </is>
+      </c>
+      <c r="H44" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="n"/>
+      <c r="J44" s="24" t="inlineStr">
+        <is>
+          <t>급여목록에 없는 약 — edi_code가 없을 때 채움</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>OC-02 · O-3</t>
+        </is>
+      </c>
+      <c r="L44" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M44" s="25" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N44" s="24" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>prescription_item_candidates</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>약품 매칭 후보</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
           <t>score</t>
         </is>
       </c>
-      <c r="D44" s="24" t="inlineStr">
+      <c r="D45" s="24" t="inlineStr">
         <is>
           <t>매칭 점수</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E45" s="24" t="inlineStr">
         <is>
           <t>decimal(5,4)</t>
         </is>
       </c>
-      <c r="F44" s="25" t="n"/>
-      <c r="G44" s="24" t="n"/>
-      <c r="H44" s="25" t="inlineStr">
+      <c r="F45" s="25" t="n"/>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I44" s="24" t="n"/>
-      <c r="J44" s="24" t="n"/>
-      <c r="K44" s="24" t="inlineStr">
+      <c r="I45" s="24" t="n"/>
+      <c r="J45" s="24" t="n"/>
+      <c r="K45" s="24" t="inlineStr">
         <is>
           <t>OC-02 · O-3</t>
         </is>
       </c>
-      <c r="L44" s="25" t="inlineStr">
+      <c r="L45" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M44" s="25" t="inlineStr">
+      <c r="M45" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N44" s="24" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>health_checkups</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>건강검진 (보류)</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G45" s="15" t="n"/>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="15" t="n"/>
-      <c r="K45" s="15" t="inlineStr">
-        <is>
-          <t>REQ-015</t>
-        </is>
-      </c>
-      <c r="L45" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M45" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N45" s="15" t="inlineStr">
-        <is>
-          <t>보류 (REQ-015 · 멘토링 확인 후 결정)</t>
-        </is>
-      </c>
+      <c r="N45" s="24" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
@@ -10842,12 +10939,12 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>사용자 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
@@ -10857,14 +10954,10 @@
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="n"/>
       <c r="H46" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10887,7 +10980,11 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N46" s="15" t="n"/>
+      <c r="N46" s="15" t="inlineStr">
+        <is>
+          <t>보류 (REQ-015 · 멘토링 확인 후 결정)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
@@ -10902,24 +10999,32 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>checkup_date</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>검진일</t>
+          <t>사용자 ID</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="15" t="n"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
       <c r="H47" s="16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I47" s="15" t="n"/>
@@ -10954,17 +11059,17 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>ocr_raw_text</t>
+          <t>checkup_date</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>OCR 원문</t>
+          <t>검진일</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="F48" s="16" t="n"/>
@@ -11006,17 +11111,17 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>ocr_raw_text</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>생성 일시</t>
+          <t>OCR 원문</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F49" s="16" t="n"/>
@@ -11026,11 +11131,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="I49" s="15" t="n"/>
       <c r="J49" s="15" t="n"/>
       <c r="K49" s="15" t="inlineStr">
         <is>
@@ -11052,41 +11153,41 @@
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>checkup_results</t>
+          <t>health_checkups</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>건강검진 결과 (보류)</t>
+          <t>건강검진 (보류)</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 일시</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="n"/>
       <c r="G50" s="15" t="n"/>
       <c r="H50" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I50" s="15" t="n"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="J50" s="15" t="n"/>
       <c r="K50" s="15" t="inlineStr">
         <is>
@@ -11103,11 +11204,7 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N50" s="15" t="inlineStr">
-        <is>
-          <t>보류 (REQ-015)</t>
-        </is>
-      </c>
+      <c r="N50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
@@ -11122,12 +11219,12 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>checkup_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>건강검진 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
@@ -11137,14 +11234,10 @@
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>health_checkups.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="n"/>
       <c r="H51" s="16" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11167,67 +11260,71 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N51" s="15" t="n"/>
+      <c r="N51" s="15" t="inlineStr">
+        <is>
+          <t>보류 (REQ-015)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>checkup_results</t>
         </is>
       </c>
-      <c r="B52" s="21" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>건강검진 결과 (보류)</t>
         </is>
       </c>
-      <c r="C52" s="21" t="inlineStr">
-        <is>
-          <t>item_code</t>
-        </is>
-      </c>
-      <c r="D52" s="21" t="inlineStr">
-        <is>
-          <t>검사 항목 코드</t>
-        </is>
-      </c>
-      <c r="E52" s="21" t="inlineStr">
-        <is>
-          <t>varchar(8)</t>
-        </is>
-      </c>
-      <c r="F52" s="22" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>checkup_id</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>건강검진 ID</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
         <is>
           <t>FK</t>
         </is>
       </c>
-      <c r="G52" s="21" t="inlineStr">
-        <is>
-          <t>checkup_items.code</t>
-        </is>
-      </c>
-      <c r="H52" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I52" s="21" t="n"/>
-      <c r="J52" s="21" t="n"/>
-      <c r="K52" s="21" t="inlineStr">
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>health_checkups.id</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="n"/>
+      <c r="J52" s="15" t="n"/>
+      <c r="K52" s="15" t="inlineStr">
         <is>
           <t>REQ-015</t>
         </is>
       </c>
-      <c r="L52" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M52" s="22" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N52" s="21" t="n"/>
+      <c r="L52" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
@@ -11242,21 +11339,29 @@
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>value_num</t>
+          <t>item_code</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>결과 수치</t>
+          <t>검사 항목 코드</t>
         </is>
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>decimal(12,3)</t>
-        </is>
-      </c>
-      <c r="F53" s="22" t="n"/>
-      <c r="G53" s="21" t="n"/>
+          <t>varchar(8)</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t>checkup_items.code</t>
+        </is>
+      </c>
       <c r="H53" s="22" t="inlineStr">
         <is>
           <t>N</t>
@@ -11294,17 +11399,17 @@
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>value_text</t>
+          <t>value_num</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
         <is>
-          <t>결과 판정</t>
+          <t>결과 수치</t>
         </is>
       </c>
       <c r="E54" s="21" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
+          <t>decimal(12,3)</t>
         </is>
       </c>
       <c r="F54" s="22" t="n"/>
@@ -11333,8 +11438,60 @@
       </c>
       <c r="N54" s="21" t="n"/>
     </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>checkup_results</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>건강검진 결과 (보류)</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>value_text</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>결과 판정</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>varchar(200)</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I55" s="21" t="n"/>
+      <c r="J55" s="21" t="n"/>
+      <c r="K55" s="21" t="inlineStr">
+        <is>
+          <t>REQ-015</t>
+        </is>
+      </c>
+      <c r="L55" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M55" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N55" s="21" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:N52"/>
+  <autoFilter ref="A4:N53"/>
   <dataValidations count="3">
     <dataValidation sqref="H5:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>

--- a/docs/planning/ERD_6기_5팀_v1.3.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.3.xlsx
@@ -910,7 +910,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -1026,82 +1025,86 @@
       <c r="H7" s="32" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>nickname</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>birth_year</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Patient.name.text</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>Patient.birthDate</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>연도만 "1955" 형식 (FHIR date는 YYYY 허용)</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H8" s="32" t="inlineStr">
+        <is>
+          <t>최소 수집 원칙과 FHIR 모두 충족</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Patient.gender</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>M → male / F → female</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>별명이라 name.use = nickname</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="C9" s="32" t="inlineStr">
-        <is>
-          <t>birth_year</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t>Patient.birthDate</t>
-        </is>
-      </c>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t>연도만 "1955" 형식 (FHIR date는 YYYY 허용)</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H9" s="32" t="inlineStr">
-        <is>
-          <t>최소 수집 원칙과 FHIR 모두 충족</t>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>AdministrativeGender 값셋</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1121,7 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>deleted_at</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
@@ -1128,12 +1131,12 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Patient.gender</t>
+          <t>Patient.active</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>M → male / F → female</t>
+          <t>탈퇴 시 active = false</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -1141,341 +1144,337 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
-        <is>
-          <t>AdministrativeGender 값셋</t>
-        </is>
-      </c>
+      <c r="H10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>Patient.active</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>탈퇴 시 active = false</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Patient.meta.lastUpdated</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr"/>
+      <c r="G11" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H11" s="32" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>login_id · password_hash · failed_login_count · locked_until</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="inlineStr"/>
+      <c r="G12" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H12" s="36" t="inlineStr">
+        <is>
+          <t>계정 · 인증 정보 (FHIR 리소스에 넣지 않음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>user_consents</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr"/>
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>동의 1건 = Consent 1개</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>Patient.meta.lastUpdated</t>
-        </is>
-      </c>
-      <c r="F12" s="32" t="inlineStr"/>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>user_consents</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Consent.patient</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>Reference(Patient)</t>
+        </is>
+      </c>
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H12" s="32" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="H14" s="32" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>login_id · password_hash · failed_login_count · locked_until</t>
-        </is>
-      </c>
-      <c r="D13" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="36" t="inlineStr"/>
-      <c r="G13" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H13" s="36" t="inlineStr">
-        <is>
-          <t>계정 · 인증 정보 (FHIR 리소스에 넣지 않음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>user_consents</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>consent_type</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>Consent.category</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>terms / privacy / sensitive_health → 자체 코드</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>국내 개인정보 동의 구분은 표준 코드 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>agreed</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Consent.provision.type</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>true → permit / false → deny</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>user_consents</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>agreed_at</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Consent.dateTime</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr"/>
+      <c r="G17" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H17" s="32" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>user_consents</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>withdrawn_at</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Consent</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Consent.status</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>철회 시 status = inactive (철회 시각은 새 Consent의 dateTime)</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
-        <is>
-          <t>동의 1건 = Consent 1개</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>user_consents</t>
-        </is>
-      </c>
-      <c r="C15" s="32" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Consent</t>
-        </is>
-      </c>
-      <c r="E15" s="32" t="inlineStr">
-        <is>
-          <t>Consent.patient</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>Reference(Patient)</t>
-        </is>
-      </c>
-      <c r="G15" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H15" s="32" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>user_consents</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>consent_type</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Consent</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>Consent.category</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>terms / privacy / sensitive_health → 자체 코드</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>국내 개인정보 동의 구분은 표준 코드 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B17" s="33" t="inlineStr">
-        <is>
-          <t>user_consents</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>agreed</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>Consent</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>Consent.provision.type</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>true → permit / false → deny</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>user_consents</t>
-        </is>
-      </c>
-      <c r="C18" s="32" t="inlineStr">
-        <is>
-          <t>agreed_at</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
-        <is>
-          <t>Consent</t>
-        </is>
-      </c>
-      <c r="E18" s="32" t="inlineStr">
-        <is>
-          <t>Consent.dateTime</t>
-        </is>
-      </c>
-      <c r="F18" s="32" t="inlineStr"/>
-      <c r="G18" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H18" s="32" t="inlineStr"/>
+      <c r="H18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>user_consents</t>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>withdrawn_at</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>Consent</t>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>MedicationRequest 묶음 · DocumentReference</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Consent.status</t>
+          <t>MedicationRequest.groupIdentifier</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>철회 시 status = inactive (철회 시각은 새 Consent의 dateTime)</t>
+          <t>처방전 1장 = 같은 groupIdentifier를 가진 MedicationRequest 여러 개</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
@@ -1483,7 +1482,11 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr"/>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>사진 · OCR 원문은 DocumentReference로 분리</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -1491,29 +1494,29 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>prescriptions</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>MedicationRequest 묶음 · DocumentReference</t>
+          <t>doc_type</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest / MedicationDispense</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.groupIdentifier</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>처방전 1장 = 같은 groupIdentifier를 가진 MedicationRequest 여러 개</t>
+          <t>prescription(처방전) → MedicationRequest / pill_bag(약봉투) → MedicationDispense</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
@@ -1523,87 +1526,83 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>사진 · OCR 원문은 DocumentReference로 분리</t>
+          <t>처방전은 "처방", 약봉투는 "조제" 기록이라 FHIR 리소스가 다름</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>prescriptions</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>doc_type</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest / MedicationDispense</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>prescription(처방전) → MedicationRequest / pill_bag(약봉투) → MedicationDispense</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>issued_date</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>MedicationRequest.authoredOn</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr"/>
+      <c r="G21" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H21" s="32" t="inlineStr">
+        <is>
+          <t>약봉투는 MedicationDispense.whenHandedOver</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>hospital_name</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.requester → Organization.name</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr"/>
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>처방전은 "처방", 약봉투는 "조제" 기록이라 FHIR 리소스가 다름</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>prescriptions</t>
-        </is>
-      </c>
-      <c r="C22" s="32" t="inlineStr">
-        <is>
-          <t>issued_date</t>
-        </is>
-      </c>
-      <c r="D22" s="32" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E22" s="32" t="inlineStr">
-        <is>
-          <t>MedicationRequest.authoredOn</t>
-        </is>
-      </c>
-      <c r="F22" s="32" t="inlineStr"/>
-      <c r="G22" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H22" s="32" t="inlineStr">
-        <is>
-          <t>약봉투는 MedicationDispense.whenHandedOver</t>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>병원을 Organization으로 참조</t>
         </is>
       </c>
     </row>
@@ -1620,20 +1619,24 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>hospital_name</t>
+          <t>ocr_raw_text</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>DocumentReference</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.requester → Organization.name</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr"/>
+          <t>DocumentReference.content.attachment</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>텍스트 첨부 (원본 이미지는 저장하지 않음)</t>
+        </is>
+      </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -1641,49 +1644,45 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>병원을 Organization으로 참조</t>
+          <t>10/15부터 원문을 저장하지 않아 비어 있음</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>prescriptions</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>ocr_raw_text</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>DocumentReference</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>DocumentReference.content.attachment</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>텍스트 첨부 (원본 이미지는 저장하지 않음)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>10/15부터 원문을 저장하지 않아 비어 있음</t>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>ocr_confidence · quality_flag</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr"/>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>OCR 품질 정보는 표준 요소 없음</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1699,7 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>ocr_confidence · quality_flag</t>
+          <t>notices</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -1713,7 +1712,7 @@
           <t>extension</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr"/>
+      <c r="F25" s="21" t="n"/>
       <c r="G25" s="22" t="inlineStr">
         <is>
           <t>확장</t>
@@ -1721,45 +1720,49 @@
       </c>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t>OCR 품질 정보는 표준 요소 없음</t>
+          <t>OCR 읽기 확인 표시는 내부 처리 정보</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B26" s="37" t="inlineStr">
-        <is>
-          <t>prescriptions</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>notices</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="22" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>OCR 읽기 확인 표시는 내부 처리 정보</t>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>ocr_jobs</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>v1.2 · OCR 비동기 작업</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1774,7 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>ocr_jobs</t>
+          <t>prescription_diseases</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -1781,17 +1784,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
+          <t>처방전 질병분류기호 1개 = Condition 1개</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
@@ -1801,7 +1804,7 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>v1.2 · OCR 비동기 작업</t>
+          <t>MedicationRequest.reasonReference로 연결</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1814,29 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>prescription_diseases</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
+          <t>disease_code</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Condition.code.coding</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>처방전 질병분류기호 1개 = Condition 1개</t>
+          <t>system = KCD (코드 시스템 URI 팀 정의 필요)</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
@@ -1843,7 +1846,7 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.reasonReference로 연결</t>
+          <t>KCD는 ICD-10 기반이라 ICD-10 코드 병기 가능</t>
         </is>
       </c>
     </row>
@@ -1860,22 +1863,22 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>disease_code</t>
+          <t>is_main</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Encounter</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Condition.code.coding</t>
+          <t>Encounter.diagnosis.rank</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>system = KCD (코드 시스템 URI 팀 정의 필요)</t>
+          <t>주상병 → rank 1</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
@@ -1885,127 +1888,127 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>KCD는 ICD-10 기반이라 ICD-10 코드 병기 가능</t>
+          <t>진료(Encounter) 정보가 없으면 extension</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>prescription_diseases</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>is_main</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>Encounter</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>Encounter.diagnosis.rank</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>주상병 → rank 1</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="F30" s="32" t="inlineStr">
+        <is>
+          <t>약 1줄 = MedicationRequest 1개</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H30" s="32" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>edi_code</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.medicationCodeableConcept.coding</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>system = 심평원 EDI 제품코드</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H30" s="15" t="inlineStr">
-        <is>
-          <t>진료(Encounter) 정보가 없으면 extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="H31" s="15" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B32" s="31" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D31" s="39" t="inlineStr">
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>raw_name</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="F31" s="32" t="inlineStr">
-        <is>
-          <t>약 1줄 = MedicationRequest 1개</t>
-        </is>
-      </c>
-      <c r="G31" s="30" t="inlineStr">
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>MedicationRequest.medicationCodeableConcept.text</t>
+        </is>
+      </c>
+      <c r="F32" s="32" t="inlineStr">
+        <is>
+          <t>OCR이 읽은 원문 약품명</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H31" s="32" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>edi_code</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest.medicationCodeableConcept.coding</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>system = 심평원 EDI 제품코드</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="inlineStr"/>
+      <c r="H32" s="32" t="inlineStr">
+        <is>
+          <t>매칭 실패해도 text는 남음</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="30" t="inlineStr">
@@ -2020,7 +2023,7 @@
       </c>
       <c r="C33" s="32" t="inlineStr">
         <is>
-          <t>raw_name</t>
+          <t>dose_per_time</t>
         </is>
       </c>
       <c r="D33" s="32" t="inlineStr">
@@ -2030,58 +2033,54 @@
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>MedicationRequest.medicationCodeableConcept.text</t>
-        </is>
-      </c>
-      <c r="F33" s="32" t="inlineStr">
-        <is>
-          <t>OCR이 읽은 원문 약품명</t>
-        </is>
-      </c>
+          <t>MedicationRequest.dosageInstruction.doseAndRate.doseQuantity</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr"/>
       <c r="G33" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H33" s="32" t="inlineStr">
-        <is>
-          <t>매칭 실패해도 text는 남음</t>
-        </is>
-      </c>
+      <c r="H33" s="32" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C34" s="32" t="inlineStr">
-        <is>
-          <t>dose_per_time</t>
-        </is>
-      </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>times_per_day</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E34" s="32" t="inlineStr">
-        <is>
-          <t>MedicationRequest.dosageInstruction.doseAndRate.doseQuantity</t>
-        </is>
-      </c>
-      <c r="F34" s="32" t="inlineStr"/>
-      <c r="G34" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H34" s="32" t="inlineStr"/>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.dosageInstruction.timing.repeat.frequency</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>period = 1, periodUnit = d</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -2096,7 +2095,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>times_per_day</t>
+          <t>total_days</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -2106,12 +2105,12 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.dosageInstruction.timing.repeat.frequency</t>
+          <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>period = 1, periodUnit = d</t>
+          <t>단위 d(일)</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
@@ -2134,7 +2133,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>total_days</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
@@ -2144,12 +2143,12 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
+          <t>MedicationRequest.dosageInstruction.timing.repeat.when</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>단위 d(일)</t>
+          <t>아침 식후 → PCM, 저녁 식후 → PCV, 취침 전 → HS 등 + text 원문</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
@@ -2172,7 +2171,7 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>guidance</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
@@ -2182,12 +2181,12 @@
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.dosageInstruction.timing.repeat.when</t>
+          <t>MedicationRequest.dosageInstruction.patientInstruction</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>아침 식후 → PCM, 저녁 식후 → PCV, 취침 전 → HS 등 + text 원문</t>
+          <t>문장 목록 → 줄바꿈으로 이어 붙인 text</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
@@ -2195,131 +2194,135 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H37" s="15" t="inlineStr"/>
+      <c r="H37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B38" s="33" t="inlineStr">
+      <c r="B38" s="37" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>guidance</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest.dosageInstruction.patientInstruction</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>문장 목록 → 줄바꿈으로 이어 붙인 text</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>match_status · match_score</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr"/>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>약품 매칭 상태는 내부 처리 정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B39" s="40" t="inlineStr">
+        <is>
+          <t>prescription_item_candidates</t>
+        </is>
+      </c>
+      <c r="C39" s="36" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="36" t="inlineStr"/>
+      <c r="G39" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H39" s="36" t="inlineStr">
+        <is>
+          <t>약품 매칭 후보 (내부 처리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>health_checkups · checkup_results</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>DiagnosticReport · Observation</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Observation.code / valueQuantity</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>검진 항목 코드 → Observation.code</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H38" s="15" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B39" s="37" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>match_status · match_score</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="F39" s="21" t="inlineStr"/>
-      <c r="G39" s="22" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H39" s="21" t="inlineStr">
-        <is>
-          <t>약품 매칭 상태는 내부 처리 정보</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="34" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B40" s="40" t="inlineStr">
-        <is>
-          <t>prescription_item_candidates</t>
-        </is>
-      </c>
-      <c r="C40" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="36" t="inlineStr"/>
-      <c r="G40" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H40" s="36" t="inlineStr">
-        <is>
-          <t>약품 매칭 후보 (내부 처리)</t>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>보류 (REQ-015)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>입력</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>health_checkups · checkup_results</t>
+          <t>analyses</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -2329,17 +2332,17 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>DiagnosticReport · Observation</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Observation.code / valueQuantity</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>검진 항목 코드 → Observation.code</t>
+          <t>분석 작업 1건 = Task 1개</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">
@@ -2349,7 +2352,7 @@
       </c>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>보류 (REQ-015)</t>
+          <t>비동기 작업 상태를 Task로 표현</t>
         </is>
       </c>
     </row>
@@ -2359,149 +2362,149 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B42" s="19" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>Task.status</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>current_step · failed_step · retry_count · error_code</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>Task.businessStatus · Task.statusReason</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr"/>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H43" s="21" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="C44" s="36" t="inlineStr">
+        <is>
+          <t>user_birth_year</t>
+        </is>
+      </c>
+      <c r="D44" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="36" t="inlineStr"/>
+      <c r="G44" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H44" s="36" t="inlineStr">
+        <is>
+          <t>분석 시점 스냅샷 (내부)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>analysis_prescriptions</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr">
-        <is>
-          <t>분석 작업 1건 = Task 1개</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Task.input</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>valueReference = MedicationRequest</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H42" s="15" t="inlineStr">
-        <is>
-          <t>비동기 작업 상태를 Task로 표현</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B43" s="33" t="inlineStr">
-        <is>
-          <t>analyses</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>Task.status</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B44" s="37" t="inlineStr">
-        <is>
-          <t>analyses</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>current_step · failed_step · retry_count · error_code</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>Task.businessStatus · Task.statusReason</t>
-        </is>
-      </c>
-      <c r="F44" s="21" t="inlineStr"/>
-      <c r="G44" s="22" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H44" s="21" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="34" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B45" s="35" t="inlineStr">
-        <is>
-          <t>analyses</t>
-        </is>
-      </c>
-      <c r="C45" s="36" t="inlineStr">
-        <is>
-          <t>user_birth_year</t>
-        </is>
-      </c>
-      <c r="D45" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="36" t="inlineStr"/>
-      <c r="G45" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H45" s="36" t="inlineStr">
-        <is>
-          <t>분석 시점 스냅샷 (내부)</t>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>분석에 넣은 처방 목록</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2516,7 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>analysis_prescriptions</t>
+          <t>analysis_diseases</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -2523,29 +2526,21 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Task.input</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr">
-        <is>
-          <t>valueReference = MedicationRequest</t>
-        </is>
-      </c>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr"/>
       <c r="G46" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H46" s="15" t="inlineStr">
-        <is>
-          <t>분석에 넣은 처방 목록</t>
-        </is>
-      </c>
+      <c r="H46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -2553,115 +2548,123 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B47" s="33" t="inlineStr">
         <is>
           <t>analysis_diseases</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
+          <t>origin</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>Condition.asserter</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>prescription → 처방전에서 옴 / user → asserter = Patient (직접 선택)</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>누가 주장한 질환인지 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B48" s="38" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr"/>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="D48" s="39" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E48" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="F48" s="32" t="inlineStr">
+        <is>
+          <t>경고 1건 = DetectedIssue 1개</t>
+        </is>
+      </c>
+      <c r="G48" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H48" s="32" t="inlineStr">
+        <is>
+          <t>FHIR에 "약물 문제 감지" 전용 리소스가 있음 — 가장 잘 맞는 부분</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B49" s="33" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>warning_type</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue.code</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H47" s="15" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B48" s="33" t="inlineStr">
-        <is>
-          <t>analysis_diseases</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>origin</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>Condition.asserter</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="inlineStr">
-        <is>
-          <t>prescription → 처방전에서 옴 / user → asserter = Patient (직접 선택)</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="inlineStr">
-        <is>
-          <t>누가 주장한 질환인지 구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B49" s="38" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D49" s="39" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="E49" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="F49" s="32" t="inlineStr">
-        <is>
-          <t>경고 1건 = DetectedIssue 1개</t>
-        </is>
-      </c>
-      <c r="G49" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H49" s="32" t="inlineStr">
-        <is>
-          <t>FHIR에 "약물 문제 감지" 전용 리소스가 있음 — 가장 잘 맞는 부분</t>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2681,7 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>warning_type</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
@@ -2688,12 +2691,12 @@
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>DetectedIssue.code</t>
+          <t>DetectedIssue.severity</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
+          <t>danger → high / caution → moderate / info → low</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
@@ -2701,49 +2704,45 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr">
-        <is>
-          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
-        </is>
-      </c>
+      <c r="H50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B51" s="33" t="inlineStr">
+      <c r="B51" s="31" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C51" s="15" t="inlineStr">
-        <is>
-          <t>severity</t>
-        </is>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>item_id_a · item_id_b</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue.severity</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>danger → high / caution → moderate / info → low</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="inlineStr"/>
+      <c r="E51" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue.implicated</t>
+        </is>
+      </c>
+      <c r="F51" s="32" t="inlineStr">
+        <is>
+          <t>Reference(MedicationRequest) 2개</t>
+        </is>
+      </c>
+      <c r="G51" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H51" s="32" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="30" t="inlineStr">
@@ -2758,7 +2757,7 @@
       </c>
       <c r="C52" s="32" t="inlineStr">
         <is>
-          <t>item_id_a · item_id_b</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="D52" s="32" t="inlineStr">
@@ -2768,12 +2767,12 @@
       </c>
       <c r="E52" s="32" t="inlineStr">
         <is>
-          <t>DetectedIssue.implicated</t>
+          <t>DetectedIssue.detail</t>
         </is>
       </c>
       <c r="F52" s="32" t="inlineStr">
         <is>
-          <t>Reference(MedicationRequest) 2개</t>
+          <t>DUR 금기 사유 원문</t>
         </is>
       </c>
       <c r="G52" s="30" t="inlineStr">
@@ -2784,116 +2783,116 @@
       <c r="H52" s="32" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B53" s="31" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C53" s="32" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="D53" s="32" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>source · notice_date</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E53" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue.detail</t>
-        </is>
-      </c>
-      <c r="F53" s="32" t="inlineStr">
-        <is>
-          <t>DUR 금기 사유 원문</t>
-        </is>
-      </c>
-      <c r="G53" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H53" s="32" t="inlineStr"/>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue.reference</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>식약처 고시 출처</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B54" s="33" t="inlineStr">
+      <c r="B54" s="37" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>source · notice_date</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue.reference</t>
-        </is>
-      </c>
-      <c r="F54" s="15" t="inlineStr">
-        <is>
-          <t>식약처 고시 출처</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="inlineStr"/>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>summary · daily_total · max_daily</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr"/>
+      <c r="G54" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H54" s="21" t="inlineStr">
+        <is>
+          <t>화면 문장 · 용량 계산값</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B55" s="37" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="C55" s="21" t="inlineStr">
-        <is>
-          <t>summary · daily_total · max_daily</t>
-        </is>
-      </c>
-      <c r="D55" s="21" t="inlineStr">
+      <c r="B55" s="40" t="inlineStr">
+        <is>
+          <t>guides</t>
+        </is>
+      </c>
+      <c r="C55" s="36" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E55" s="21" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="F55" s="21" t="inlineStr"/>
-      <c r="G55" s="22" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H55" s="21" t="inlineStr">
-        <is>
-          <t>화면 문장 · 용량 계산값</t>
+      <c r="E55" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="36" t="inlineStr"/>
+      <c r="G55" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H55" s="36" t="inlineStr">
+        <is>
+          <t>AI 생성 안내문 (의료 기록 아님). 필요하면 DocumentReference로 보관</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2904,7 @@
       </c>
       <c r="B56" s="40" t="inlineStr">
         <is>
-          <t>guides</t>
+          <t>feedbacks</t>
         </is>
       </c>
       <c r="C56" s="36" t="inlineStr">
@@ -2931,19 +2930,19 @@
       </c>
       <c r="H56" s="36" t="inlineStr">
         <is>
-          <t>AI 생성 안내문 (의료 기록 아님). 필요하면 DocumentReference로 보관</t>
+          <t>서비스 피드백</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>챗봇</t>
         </is>
       </c>
       <c r="B57" s="40" t="inlineStr">
         <is>
-          <t>feedbacks</t>
+          <t>chat_sessions</t>
         </is>
       </c>
       <c r="C57" s="36" t="inlineStr">
@@ -2969,45 +2968,45 @@
       </c>
       <c r="H57" s="36" t="inlineStr">
         <is>
-          <t>서비스 피드백</t>
+          <t>대화 묶음 (내부)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="34" t="inlineStr">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>챗봇</t>
         </is>
       </c>
-      <c r="B58" s="40" t="inlineStr">
-        <is>
-          <t>chat_sessions</t>
-        </is>
-      </c>
-      <c r="C58" s="36" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="36" t="inlineStr"/>
-      <c r="G58" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H58" s="36" t="inlineStr">
-        <is>
-          <t>대화 묶음 (내부)</t>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="inlineStr"/>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>의료 기록으로 보관할 필요가 생길 때만</t>
         </is>
       </c>
     </row>
@@ -3017,24 +3016,24 @@
           <t>챗봇</t>
         </is>
       </c>
-      <c r="B59" s="19" t="inlineStr">
+      <c r="B59" s="33" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
+          <t>role · content · created_at</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Communication.sender · payload.contentString · sent</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr"/>
@@ -3043,39 +3042,39 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H59" s="15" t="inlineStr">
-        <is>
-          <t>의료 기록으로 보관할 필요가 생길 때만</t>
-        </is>
-      </c>
+      <c r="H59" s="15" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>챗봇</t>
-        </is>
-      </c>
-      <c r="B60" s="33" t="inlineStr">
-        <is>
-          <t>chat_messages</t>
+          <t>실천·보상</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>role · content · created_at</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>Communication</t>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>CarePlan</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Communication.sender · payload.contentString · sent</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr"/>
+          <t>CarePlan.activity</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>추천 1개 = activity 1개 (status = not-started)</t>
+        </is>
+      </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3084,42 +3083,42 @@
       <c r="H60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>recommendations</t>
-        </is>
-      </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
+        <is>
+          <t>habit_goals</t>
+        </is>
+      </c>
+      <c r="C61" s="32" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D61" s="14" t="inlineStr">
-        <is>
-          <t>CarePlan</t>
-        </is>
-      </c>
-      <c r="E61" s="15" t="inlineStr">
-        <is>
-          <t>CarePlan.activity</t>
-        </is>
-      </c>
-      <c r="F61" s="15" t="inlineStr">
-        <is>
-          <t>추천 1개 = activity 1개 (status = not-started)</t>
-        </is>
-      </c>
-      <c r="G61" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="inlineStr"/>
+      <c r="D61" s="39" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="E61" s="32" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="F61" s="32" t="inlineStr"/>
+      <c r="G61" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H61" s="32" t="inlineStr">
+        <is>
+          <t>FHIR Goal = 환자 건강 목표</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="30" t="inlineStr">
@@ -3127,24 +3126,24 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B62" s="38" t="inlineStr">
+      <c r="B62" s="31" t="inlineStr">
         <is>
           <t>habit_goals</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D62" s="39" t="inlineStr">
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Goal.description.text</t>
         </is>
       </c>
       <c r="F62" s="32" t="inlineStr"/>
@@ -3153,11 +3152,7 @@
           <t>일치</t>
         </is>
       </c>
-      <c r="H62" s="32" t="inlineStr">
-        <is>
-          <t>FHIR Goal = 환자 건강 목표</t>
-        </is>
-      </c>
+      <c r="H62" s="32" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="30" t="inlineStr">
@@ -3172,7 +3167,7 @@
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>target_value · unit</t>
         </is>
       </c>
       <c r="D63" s="32" t="inlineStr">
@@ -3182,7 +3177,7 @@
       </c>
       <c r="E63" s="32" t="inlineStr">
         <is>
-          <t>Goal.description.text</t>
+          <t>Goal.target.detailQuantity</t>
         </is>
       </c>
       <c r="F63" s="32" t="inlineStr"/>
@@ -3206,7 +3201,7 @@
       </c>
       <c r="C64" s="32" t="inlineStr">
         <is>
-          <t>target_value · unit</t>
+          <t>start_date · end_date</t>
         </is>
       </c>
       <c r="D64" s="32" t="inlineStr">
@@ -3216,7 +3211,7 @@
       </c>
       <c r="E64" s="32" t="inlineStr">
         <is>
-          <t>Goal.target.detailQuantity</t>
+          <t>Goal.startDate · Goal.target.dueDate</t>
         </is>
       </c>
       <c r="F64" s="32" t="inlineStr"/>
@@ -3228,38 +3223,42 @@
       <c r="H64" s="32" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B65" s="31" t="inlineStr">
+      <c r="B65" s="33" t="inlineStr">
         <is>
           <t>habit_goals</t>
         </is>
       </c>
-      <c r="C65" s="32" t="inlineStr">
-        <is>
-          <t>start_date · end_date</t>
-        </is>
-      </c>
-      <c r="D65" s="32" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="E65" s="32" t="inlineStr">
-        <is>
-          <t>Goal.startDate · Goal.target.dueDate</t>
-        </is>
-      </c>
-      <c r="F65" s="32" t="inlineStr"/>
-      <c r="G65" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H65" s="32" t="inlineStr"/>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>Goal.lifecycleStatus</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>active → active / ended → completed</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -3267,29 +3266,29 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B66" s="33" t="inlineStr">
-        <is>
-          <t>habit_goals</t>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>habit_records</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>Goal</t>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>Observation</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Goal.lifecycleStatus</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>active → active / ended → completed</t>
+          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr">
@@ -3305,109 +3304,105 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B67" s="19" t="inlineStr">
+      <c r="B67" s="33" t="inlineStr">
         <is>
           <t>habit_records</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
+          <t>value · completed · record_date</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>Observation.valueQuantity / valueBoolean · effectiveDateTime</t>
+        </is>
+      </c>
+      <c r="F67" s="15" t="inlineStr"/>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>실천·보상</t>
+        </is>
+      </c>
+      <c r="B68" s="40" t="inlineStr">
+        <is>
+          <t>rewards</t>
+        </is>
+      </c>
+      <c r="C68" s="36" t="inlineStr">
+        <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="E67" s="15" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="F67" s="15" t="inlineStr">
-        <is>
-          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
-        </is>
-      </c>
-      <c r="G67" s="16" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="36" t="inlineStr"/>
+      <c r="G68" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>포인트 (서비스 보상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>drug_products</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>Medication</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>Medication</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="inlineStr"/>
+      <c r="G69" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H67" s="15" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B68" s="33" t="inlineStr">
-        <is>
-          <t>habit_records</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>value · completed · record_date</t>
-        </is>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>Observation.valueQuantity / valueBoolean · effectiveDateTime</t>
-        </is>
-      </c>
-      <c r="F68" s="15" t="inlineStr"/>
-      <c r="G68" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="34" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B69" s="40" t="inlineStr">
-        <is>
-          <t>rewards</t>
-        </is>
-      </c>
-      <c r="C69" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="36" t="inlineStr"/>
-      <c r="G69" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H69" s="36" t="inlineStr">
-        <is>
-          <t>포인트 (서비스 보상)</t>
-        </is>
-      </c>
+      <c r="H69" s="15" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -3415,27 +3410,31 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B70" s="19" t="inlineStr">
+      <c r="B70" s="33" t="inlineStr">
         <is>
           <t>drug_products</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr">
+          <t>edi_code</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
         <is>
           <t>Medication</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="F70" s="15" t="inlineStr"/>
+          <t>Medication.code.coding</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>system = 심평원 EDI 제품코드</t>
+        </is>
+      </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3456,7 +3455,7 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>edi_code</t>
+          <t>ingr_code</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
@@ -3466,12 +3465,12 @@
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Medication.code.coding</t>
+          <t>Medication.ingredient.itemCodeableConcept</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>system = 심평원 EDI 제품코드</t>
+          <t>system = 심평원 주성분코드</t>
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr">
@@ -3494,24 +3493,20 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>ingr_code</t>
+          <t>entp_name</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>Medication</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Medication.ingredient.itemCodeableConcept</t>
-        </is>
-      </c>
-      <c r="F72" s="15" t="inlineStr">
-        <is>
-          <t>system = 심평원 주성분코드</t>
-        </is>
-      </c>
+          <t>Medication.manufacturer → Organization.name</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr"/>
       <c r="G72" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3532,17 +3527,17 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>entp_name</t>
+          <t>spec_value · spec_unit</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>Medication.manufacturer → Organization.name</t>
+          <t>Medication.ingredient.strength</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr"/>
@@ -3559,24 +3554,24 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B74" s="33" t="inlineStr">
-        <is>
-          <t>drug_products</t>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>drug_ingredients</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>spec_value · spec_unit</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>Medication</t>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>Substance</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Medication.ingredient.strength</t>
+          <t>Substance.code</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr"/>
@@ -3595,7 +3590,7 @@
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>drug_ingredients</t>
+          <t>drug_details</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
@@ -3605,21 +3600,29 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>Substance</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>Substance.code</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="inlineStr"/>
+          <t>MedicationKnowledge</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>효능효과 · 용법용량 · 주의사항</t>
+        </is>
+      </c>
       <c r="G75" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H75" s="15" t="inlineStr"/>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>RAG 검색 원문</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -3629,7 +3632,7 @@
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>drug_details</t>
+          <t>dur_interaction · dur_interaction_exception</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
@@ -3639,17 +3642,17 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>MedicationKnowledge</t>
+          <t>ClinicalUseDefinition (R5)</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>MedicationKnowledge</t>
+          <t>ClinicalUseDefinition.interaction</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>효능효과 · 용법용량 · 주의사항</t>
+          <t>type = interaction</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
@@ -3659,7 +3662,7 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>RAG 검색 원문</t>
+          <t>R4에는 전용 리소스 없음 — R5 참고</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3674,7 @@
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>dur_interaction · dur_interaction_exception</t>
+          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
@@ -3686,12 +3689,12 @@
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.interaction</t>
+          <t>ClinicalUseDefinition.contraindication</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>type = interaction</t>
+          <t>type = contraindication, population = 나이 · 임부</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
@@ -3701,7 +3704,7 @@
       </c>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>R4에는 전용 리소스 없음 — R5 참고</t>
+          <t>R5 참고</t>
         </is>
       </c>
     </row>
@@ -3713,7 +3716,7 @@
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
+          <t>dur_dose_limit</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
@@ -3723,17 +3726,17 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition (R5)</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.contraindication</t>
+          <t>MedicationKnowledge.administrationGuidelines.dosage</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>type = contraindication, population = 나이 · 임부</t>
+          <t>1일 최대 투여량</t>
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr">
@@ -3741,87 +3744,83 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H78" s="15" t="inlineStr">
-        <is>
-          <t>R5 참고</t>
-        </is>
-      </c>
+      <c r="H78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+      <c r="A79" s="34" t="inlineStr">
         <is>
           <t>마스터</t>
         </is>
       </c>
-      <c r="B79" s="19" t="inlineStr">
-        <is>
-          <t>dur_dose_limit</t>
-        </is>
-      </c>
-      <c r="C79" s="15" t="inlineStr">
+      <c r="B79" s="40" t="inlineStr">
+        <is>
+          <t>dup_ingredient · dup_efficacy</t>
+        </is>
+      </c>
+      <c r="C79" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>MedicationKnowledge</t>
-        </is>
-      </c>
-      <c r="E79" s="15" t="inlineStr">
-        <is>
-          <t>MedicationKnowledge.administrationGuidelines.dosage</t>
-        </is>
-      </c>
-      <c r="F79" s="15" t="inlineStr">
-        <is>
-          <t>1일 최대 투여량</t>
-        </is>
-      </c>
-      <c r="G79" s="16" t="inlineStr">
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="36" t="inlineStr"/>
+      <c r="G79" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>국내 DUR 중복 점검 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>diseases</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>CodeSystem</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>CodeSystem.concept</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>KCD 상병 코드 목록</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H79" s="15" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="34" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B80" s="40" t="inlineStr">
-        <is>
-          <t>dup_ingredient · dup_efficacy</t>
-        </is>
-      </c>
-      <c r="C80" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="36" t="inlineStr"/>
-      <c r="G80" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H80" s="36" t="inlineStr">
-        <is>
-          <t>국내 DUR 중복 점검 규칙</t>
-        </is>
-      </c>
+      <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -3831,7 +3830,7 @@
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>diseases</t>
+          <t>checkup_items</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
@@ -3851,7 +3850,7 @@
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>KCD 상병 코드 목록</t>
+          <t>건강검진 검사항목 코드 목록</t>
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr">
@@ -3859,7 +3858,11 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H81" s="15" t="inlineStr"/>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -3869,7 +3872,7 @@
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>checkup_items</t>
+          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -3879,19 +3882,15 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>CodeSystem</t>
+          <t>PlanDefinition</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>CodeSystem.concept</t>
-        </is>
-      </c>
-      <c r="F82" s="15" t="inlineStr">
-        <is>
-          <t>건강검진 검사항목 코드 목록</t>
-        </is>
-      </c>
+          <t>PlanDefinition.action</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr"/>
       <c r="G82" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3899,7 +3898,7 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>보류</t>
+          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3910,7 @@
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
-          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
+          <t>lifestyle_guide_sources</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
@@ -3921,15 +3920,19 @@
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>PlanDefinition</t>
+          <t>DocumentReference / Citation (R5)</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>PlanDefinition.action</t>
-        </is>
-      </c>
-      <c r="F83" s="15" t="inlineStr"/>
+          <t>PlanDefinition.relatedArtifact</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>type = citation · display = 문서명 · url · citation = 기관 · 발행일</t>
+        </is>
+      </c>
       <c r="G83" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3937,87 +3940,83 @@
       </c>
       <c r="H83" s="15" t="inlineStr">
         <is>
-          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
+          <t>v1.2 · R4는 relatedArtifact로 출처 표시</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="inlineStr">
+      <c r="A84" s="22" t="inlineStr">
         <is>
           <t>마스터</t>
         </is>
       </c>
-      <c r="B84" s="19" t="inlineStr">
-        <is>
-          <t>lifestyle_guide_sources</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="inlineStr">
+      <c r="B84" s="37" t="inlineStr">
+        <is>
+          <t>lifestyle_medication_links</t>
+        </is>
+      </c>
+      <c r="C84" s="21" t="inlineStr">
+        <is>
+          <t>requires_clinician · goal_eligible</t>
+        </is>
+      </c>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="21" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F84" s="21" t="inlineStr"/>
+      <c r="G84" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H84" s="21" t="inlineStr">
+        <is>
+          <t>v1.2 · 서비스 표시 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="34" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B85" s="40" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="C85" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D84" s="14" t="inlineStr">
-        <is>
-          <t>DocumentReference / Citation (R5)</t>
-        </is>
-      </c>
-      <c r="E84" s="15" t="inlineStr">
-        <is>
-          <t>PlanDefinition.relatedArtifact</t>
-        </is>
-      </c>
-      <c r="F84" s="15" t="inlineStr">
-        <is>
-          <t>type = citation · display = 문서명 · url · citation = 기관 · 발행일</t>
-        </is>
-      </c>
-      <c r="G84" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H84" s="15" t="inlineStr">
-        <is>
-          <t>v1.2 · R4는 relatedArtifact로 출처 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="22" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B85" s="37" t="inlineStr">
-        <is>
-          <t>lifestyle_medication_links</t>
-        </is>
-      </c>
-      <c r="C85" s="21" t="inlineStr">
-        <is>
-          <t>requires_clinician · goal_eligible</t>
-        </is>
-      </c>
-      <c r="D85" s="21" t="inlineStr">
+      <c r="D85" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E85" s="21" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="F85" s="21" t="inlineStr"/>
-      <c r="G85" s="22" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H85" s="21" t="inlineStr">
-        <is>
-          <t>v1.2 · 서비스 표시 규칙</t>
+      <c r="E85" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="36" t="n"/>
+      <c r="G85" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H85" s="36" t="inlineStr">
+        <is>
+          <t>미리 저장해 두는 AI 생성 약 안내문 (의료 기록 아님). guides와 같은 이유로 FHIR 대응 없음</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4037,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7090,6 +7089,84 @@
         </is>
       </c>
       <c r="E158" s="10" t="n"/>
+    </row>
+    <row r="159" hidden="1" outlineLevel="1">
+      <c r="A159" s="10" t="n"/>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>사용자 / users.nickname — 필드 삭제</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>nickname varchar(50) · N — 선택 입력. 홈 인사말용</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>삭제
+사유: 홈 인사말을 뺌(3회차 멘토링 · 10/7 회의). 인사말용 별명이 쓸 곳이 없어 최소 수집 원칙에 맞춰 뺌 (10/14 팀 합의 · #96). 가입 · 로그인 · 내 정보 응답에서도 뺌</t>
+        </is>
+      </c>
+      <c r="E159" s="10" t="n"/>
+    </row>
+    <row r="160" hidden="1" outlineLevel="1">
+      <c r="A160" s="10" t="n"/>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>FHIR 대응 탭 — users.nickname 행 삭제</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>80행 — nickname → Patient.name.text</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="inlineStr">
+        <is>
+          <t>79행 — 칸이 없어져 대응 행도 뺌</t>
+        </is>
+      </c>
+      <c r="E160" s="10" t="n"/>
+    </row>
+    <row r="161" hidden="1" outlineLevel="1">
+      <c r="A161" s="10" t="n"/>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>분석 / drug_guides — 테이블 신규</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>(없음) — 안내문은 분석 때마다 guides에 만들었음</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>필드 10개: edi_code(PK), content, evidence_ids, prompt_ver, model_name, review_status, reviewed_by, reviewed_at, created_at, updated_at
+사유: 멘토링 4회차(10/13) · 10/14 팀 합의 — 안내문을 약 단위로 미리 저장하고 사람이 확인한 것만 분석에 씀. 근거 번호와 출처를 같이 저장해 챗봇이 그대로 씀</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="n"/>
+    </row>
+    <row r="162" hidden="1" outlineLevel="1">
+      <c r="A162" s="10" t="n"/>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>FHIR 대응 탭 — drug_guides 행 추가</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>79행</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="inlineStr">
+        <is>
+          <t>80행 — drug_guides (테이블) · FHIR 외 (guides와 같음)</t>
+        </is>
+      </c>
+      <c r="E162" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7372,7 +7449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7662,30 +7739,30 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>nickname</t>
+          <t>birth_year</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>이름 (별명)</t>
+          <t>출생연도</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr"/>
       <c r="G8" s="21" t="inlineStr"/>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t>선택 입력. 홈 인사말용</t>
+          <t>생년월일 대신 출생연도만 (최소 수집) · 노인주의 · 연령금기 판정</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -7718,17 +7795,17 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>birth_year</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>출생연도</t>
+          <t>성별</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>varchar(1)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr"/>
@@ -7741,7 +7818,7 @@
       <c r="I9" s="21" t="inlineStr"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>생년월일 대신 출생연도만 (최소 수집) · 노인주의 · 연령금기 판정</t>
+          <t>M / F</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -7762,60 +7839,64 @@
       <c r="N9" s="21" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>sex</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>성별</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>varchar(1)</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr"/>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t>M / F</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>failed_login_count</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>로그인 실패 횟수</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>smallint</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr"/>
+      <c r="G10" s="24" t="inlineStr"/>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t>5회 실패 시 잠금 (CM-01-E1)</t>
+        </is>
+      </c>
+      <c r="K10" s="24" t="inlineStr">
         <is>
           <t>CM-01~07 · A-1~3 · U-1~3</t>
         </is>
       </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M10" s="22" t="inlineStr">
+      <c r="L10" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N10" s="21" t="inlineStr"/>
+      <c r="N10" s="24" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
@@ -7830,17 +7911,17 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>failed_login_count</t>
+          <t>locked_until</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>로그인 실패 횟수</t>
+          <t>잠금 해제 시각</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr"/>
@@ -7850,14 +7931,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I11" s="24" t="inlineStr"/>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>5회 실패 시 잠금 (CM-01-E1)</t>
+          <t>잠금 해제 시각 (CM-01-E2)</t>
         </is>
       </c>
       <c r="K11" s="24" t="inlineStr">
@@ -7878,224 +7955,228 @@
       <c r="N11" s="24" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>locked_until</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>잠금 해제 시각</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr"/>
-      <c r="G12" s="24" t="inlineStr"/>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="15" t="inlineStr"/>
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr"/>
-      <c r="J12" s="24" t="inlineStr">
-        <is>
-          <t>잠금 해제 시각 (CM-01-E2)</t>
-        </is>
-      </c>
-      <c r="K12" s="24" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr"/>
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t>CM-01~07 · A-1~3 · U-1~3</t>
         </is>
       </c>
-      <c r="L12" s="25" t="inlineStr">
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>기존</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>v0.1</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr"/>
+      <c r="G13" s="24" t="inlineStr"/>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr"/>
+      <c r="J13" s="24" t="inlineStr"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>CM-01~07 · A-1~3 · U-1~3</t>
+        </is>
+      </c>
+      <c r="L13" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M12" s="25" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N12" s="24" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="N13" s="24" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>생성 일시</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>탈퇴 일시</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="15" t="inlineStr"/>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr"/>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>탈퇴 시 개인정보 파기 후 시각만 남김 (CM-07)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
         <is>
           <t>CM-01~07 · A-1~3 · U-1~3</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>기존</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>v0.1</t>
-        </is>
-      </c>
-      <c r="N13" s="15" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>회원</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>수정 일시</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F14" s="25" t="inlineStr"/>
-      <c r="G14" s="24" t="inlineStr"/>
-      <c r="H14" s="25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="inlineStr"/>
-      <c r="J14" s="24" t="inlineStr"/>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>CM-01~07 · A-1~3 · U-1~3</t>
-        </is>
-      </c>
-      <c r="L14" s="25" t="inlineStr">
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>user_consents</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>동의 기록</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr"/>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr"/>
+      <c r="J15" s="24" t="inlineStr"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
+        </is>
+      </c>
+      <c r="L15" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M14" s="25" t="inlineStr">
+      <c r="M15" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N14" s="24" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>회원</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>탈퇴 일시</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr"/>
-      <c r="G15" s="21" t="inlineStr"/>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>탈퇴 시 개인정보 파기 후 시각만 남김 (CM-07)</t>
-        </is>
-      </c>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t>CM-01~07 · A-1~3 · U-1~3</t>
-        </is>
-      </c>
-      <c r="L15" s="22" t="inlineStr">
-        <is>
-          <t>수정</t>
-        </is>
-      </c>
-      <c r="M15" s="22" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N15" s="21" t="inlineStr"/>
+      <c r="N15" s="24" t="inlineStr">
+        <is>
+          <t>v1.0 신규 · CM-02 가입 동의, CM-05 동의 내역</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
@@ -8110,12 +8191,12 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>사용자 ID</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -8125,10 +8206,14 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr"/>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8151,11 +8236,7 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N16" s="24" t="inlineStr">
-        <is>
-          <t>v1.0 신규 · CM-02 가입 동의, CM-05 동의 내역</t>
-        </is>
-      </c>
+      <c r="N16" s="24" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
@@ -8170,36 +8251,32 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>consent_type</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>사용자 ID</t>
+          <t>동의 종류</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr"/>
+      <c r="G17" s="24" t="inlineStr"/>
       <c r="H17" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr"/>
-      <c r="J17" s="24" t="inlineStr"/>
+      <c r="J17" s="24" t="inlineStr">
+        <is>
+          <t>terms / privacy / sensitive_health</t>
+        </is>
+      </c>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
@@ -8230,17 +8307,17 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>consent_type</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>동의 종류</t>
+          <t>동의 여부</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F18" s="25" t="inlineStr"/>
@@ -8251,11 +8328,7 @@
         </is>
       </c>
       <c r="I18" s="24" t="inlineStr"/>
-      <c r="J18" s="24" t="inlineStr">
-        <is>
-          <t>terms / privacy / sensitive_health</t>
-        </is>
-      </c>
+      <c r="J18" s="24" t="inlineStr"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
@@ -8286,24 +8359,24 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>agreed_at</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>동의 여부</t>
+          <t>동의 일시</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr"/>
       <c r="G19" s="24" t="inlineStr"/>
       <c r="H19" s="25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I19" s="24" t="inlineStr"/>
@@ -8338,12 +8411,12 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>agreed_at</t>
+          <t>withdrawn_at</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>동의 일시</t>
+          <t>철회 일시</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -8359,7 +8432,11 @@
         </is>
       </c>
       <c r="I20" s="24" t="inlineStr"/>
-      <c r="J20" s="24" t="inlineStr"/>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>철회 시각. sensitive_health 철회 시 업로드 · 분석 불가 (🟡 기존 기록 처리 팀 결정)</t>
+        </is>
+      </c>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
@@ -8375,63 +8452,7 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N20" s="24" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>user_consents</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>동의 기록</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>withdrawn_at</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>철회 일시</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="inlineStr"/>
-      <c r="G21" s="24" t="inlineStr"/>
-      <c r="H21" s="25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr"/>
-      <c r="J21" s="24" t="inlineStr">
-        <is>
-          <t>철회 시각. sensitive_health 철회 시 업로드 · 분석 불가 (🟡 기존 기록 처리 팀 결정)</t>
-        </is>
-      </c>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
-        </is>
-      </c>
-      <c r="L21" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M21" s="25" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N21" s="24" t="inlineStr">
+      <c r="N20" s="24" t="inlineStr">
         <is>
           <t>인덱스: (user_id, consent_type) [unique]</t>
         </is>
@@ -8493,7 +8514,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -11513,7 +11533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14069,6 +14089,570 @@
         </is>
       </c>
       <c r="N47" s="15" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>edi_code</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>약 코드</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="n"/>
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="n"/>
+      <c r="J48" s="15" t="inlineStr">
+        <is>
+          <t>약제급여목록 제품코드(EDI). 약 1개 = 1행. 급여목록에 없는 약은 행이 없음</t>
+        </is>
+      </c>
+      <c r="K48" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L48" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N48" s="15" t="inlineStr">
+        <is>
+          <t>멘토링 4회차(10/13) · 10/14 팀 합의. 약 단위로 미리 만들어 두고 사람이 확인한 것만 분석에 씀. 약 1개 = 1행 (약효분류 표로 만든 안내문과 허가정보 문장이 같은 표에 들어감)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>안내 내용 (JSON)</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="15" t="n"/>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="n"/>
+      <c r="J49" s="15" t="inlineStr">
+        <is>
+          <t>category · purpose · caution(문장을 줄바꿈으로 이은 문자열) · cautions(문장 배열) · source. 먹는 법은 처방마다 달라 여기 두지 않음</t>
+        </is>
+      </c>
+      <c r="K49" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L49" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N49" s="15" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>evidence_ids</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>근거 목록</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="n"/>
+      <c r="J50" s="15" t="inlineStr">
+        <is>
+          <t>[{kind: hira_class | drug_details, key, label, field(문장 번호), use(purpose · caution1~3), text(원문 문장)}] — 챗봇이 출처를 붙일 때 그대로 씀</t>
+        </is>
+      </c>
+      <c r="K50" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L50" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N50" s="15" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>prompt_ver</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>프롬프트 버전</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="n"/>
+      <c r="J51" s="15" t="inlineStr">
+        <is>
+          <t>규칙 표로 만든 것은 rule-v1, AI 문장은 med-v8</t>
+        </is>
+      </c>
+      <c r="K51" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L51" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N51" s="15" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>모델 이름</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="n"/>
+      <c r="J52" s="15" t="inlineStr">
+        <is>
+          <t>AI 없이 규칙 표로 만든 안내문은 null. 값이 있으면 허가정보 문장(AI가 쓰고 규칙으로 걸러 냄)</t>
+        </is>
+      </c>
+      <c r="K52" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L52" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N52" s="15" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>review_status</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>확인 상태</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>varchar(20)</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="J53" s="15" t="inlineStr">
+        <is>
+          <t>draft / approved / rejected — 분석 때는 approved만 보여 줌 (멘토링 4회차 · 사람 확인 필수)</t>
+        </is>
+      </c>
+      <c r="K53" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N53" s="15" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>reviewed_by</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>확인한 사람</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="n"/>
+      <c r="J54" s="15" t="n"/>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N54" s="15" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>reviewed_at</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>확인 일시</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="n"/>
+      <c r="J55" s="15" t="n"/>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L55" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N55" s="15" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>생성 일시</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="15" t="n"/>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J56" s="15" t="n"/>
+      <c r="K56" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L56" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N56" s="15" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>drug_guides</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>약 안내문 (사전 저장)</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="n"/>
+      <c r="G57" s="15" t="n"/>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="J57" s="15" t="n"/>
+      <c r="K57" s="15" t="inlineStr">
+        <is>
+          <t>RG-04 · R-4 · 챗봇 출처</t>
+        </is>
+      </c>
+      <c r="L57" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="N57" s="15" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N47"/>

--- a/docs/planning/ERD_6기_5팀_v1.3.xlsx
+++ b/docs/planning/ERD_6기_5팀_v1.3.xlsx
@@ -910,6 +910,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
@@ -1025,86 +1026,82 @@
       <c r="H7" s="32" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>nickname</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Patient.name.text</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>별명이라 name.use = nickname</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>birth_year</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Patient.birthDate</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>연도만 "1955" 형식 (FHIR date는 YYYY 허용)</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H8" s="32" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>최소 수집 원칙과 FHIR 모두 충족</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>sex</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Patient</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>Patient.gender</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>M → male / F → female</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>AdministrativeGender 값셋</t>
         </is>
       </c>
     </row>
@@ -1121,360 +1118,364 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Patient.gender</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>M → male / F → female</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>AdministrativeGender 값셋</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
           <t>deleted_at</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Patient.active</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>탈퇴 시 active = false</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Patient.meta.lastUpdated</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr"/>
-      <c r="G11" s="30" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr"/>
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H11" s="32" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>login_id · password_hash · failed_login_count · locked_until</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="36" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr"/>
-      <c r="G12" s="34" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr"/>
+      <c r="G13" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H12" s="36" t="inlineStr">
+      <c r="H13" s="36" t="inlineStr">
         <is>
           <t>계정 · 인증 정보 (FHIR 리소스에 넣지 않음)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr"/>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr"/>
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>동의 1건 = Consent 1개</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>Consent.patient</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>Reference(Patient)</t>
         </is>
       </c>
-      <c r="G14" s="30" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H14" s="32" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="H15" s="32" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>consent_type</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>Consent.category</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>terms / privacy / sensitive_health → 자체 코드</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>국내 개인정보 동의 구분은 표준 코드 없음</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>agreed</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Consent.provision.type</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>true → permit / false → deny</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>agreed_at</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>Consent.dateTime</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr"/>
-      <c r="G17" s="30" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr"/>
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H17" s="32" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>user_consents</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>withdrawn_at</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>Consent</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>Consent.status</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>철회 시 status = inactive (철회 시각은 새 Consent의 dateTime)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="inlineStr"/>
+      <c r="H18" s="32" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>prescriptions</t>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>user_consents</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>MedicationRequest 묶음 · DocumentReference</t>
+          <t>withdrawn_at</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Consent</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.groupIdentifier</t>
+          <t>Consent.status</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>처방전 1장 = 같은 groupIdentifier를 가진 MedicationRequest 여러 개</t>
+          <t>철회 시 status = inactive (철회 시각은 새 Consent의 dateTime)</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
@@ -1482,11 +1483,7 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
-        <is>
-          <t>사진 · OCR 원문은 DocumentReference로 분리</t>
-        </is>
-      </c>
+      <c r="H19" s="15" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -1494,115 +1491,119 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>prescriptions</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>MedicationRequest 묶음 · DocumentReference</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.groupIdentifier</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>처방전 1장 = 같은 groupIdentifier를 가진 MedicationRequest 여러 개</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>사진 · OCR 원문은 DocumentReference로 분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
           <t>doc_type</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest / MedicationDispense</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>prescription(처방전) → MedicationRequest / pill_bag(약봉투) → MedicationDispense</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>처방전은 "처방", 약봉투는 "조제" 기록이라 FHIR 리소스가 다름</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>prescriptions</t>
         </is>
       </c>
-      <c r="C21" s="32" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>issued_date</t>
         </is>
       </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest.authoredOn</t>
         </is>
       </c>
-      <c r="F21" s="32" t="inlineStr"/>
-      <c r="G21" s="30" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr"/>
+      <c r="G22" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H21" s="32" t="inlineStr">
+      <c r="H22" s="32" t="inlineStr">
         <is>
           <t>약봉투는 MedicationDispense.whenHandedOver</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>prescriptions</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>hospital_name</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Organization</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest.requester → Organization.name</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr"/>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="inlineStr">
-        <is>
-          <t>병원을 Organization으로 참조</t>
         </is>
       </c>
     </row>
@@ -1619,70 +1620,70 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
+          <t>hospital_name</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.requester → Organization.name</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr"/>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>병원을 Organization으로 참조</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
           <t>ocr_raw_text</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>DocumentReference</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>DocumentReference.content.attachment</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>텍스트 첨부 (원본 이미지는 저장하지 않음)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="H24" s="15" t="inlineStr">
         <is>
           <t>10/15부터 원문을 저장하지 않아 비어 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>prescriptions</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>ocr_confidence · quality_flag</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>extension</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr"/>
-      <c r="G24" s="22" t="inlineStr">
-        <is>
-          <t>확장</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>OCR 품질 정보는 표준 요소 없음</t>
         </is>
       </c>
     </row>
@@ -1699,70 +1700,66 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
+          <t>ocr_confidence · quality_flag</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr"/>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>OCR 품질 정보는 표준 요소 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>prescriptions</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
           <t>notices</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>OCR 읽기 확인 표시는 내부 처리 정보</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>ocr_jobs</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>v1.2 · OCR 비동기 작업</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1771,7 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>prescription_diseases</t>
+          <t>ocr_jobs</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -1784,17 +1781,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>처방전 질병분류기호 1개 = Condition 1개</t>
+          <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
@@ -1804,7 +1801,7 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.reasonReference로 연결</t>
+          <t>v1.2 · OCR 비동기 작업</t>
         </is>
       </c>
     </row>
@@ -1814,29 +1811,29 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>prescription_diseases</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>disease_code</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Condition.code.coding</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>system = KCD (코드 시스템 URI 팀 정의 필요)</t>
+          <t>처방전 질병분류기호 1개 = Condition 1개</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
@@ -1846,7 +1843,7 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>KCD는 ICD-10 기반이라 ICD-10 코드 병기 가능</t>
+          <t>MedicationRequest.reasonReference로 연결</t>
         </is>
       </c>
     </row>
@@ -1863,152 +1860,152 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
+          <t>disease_code</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Condition.code.coding</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>system = KCD (코드 시스템 URI 팀 정의 필요)</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>KCD는 ICD-10 기반이라 ICD-10 코드 병기 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>prescription_diseases</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
           <t>is_main</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D30" s="15" t="inlineStr">
         <is>
           <t>Encounter</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Encounter.diagnosis.rank</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>주상병 → rank 1</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H29" s="15" t="inlineStr">
+      <c r="H30" s="15" t="inlineStr">
         <is>
           <t>진료(Encounter) 정보가 없으면 extension</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D30" s="39" t="inlineStr">
+      <c r="D31" s="39" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E30" s="32" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="F30" s="32" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>약 1줄 = MedicationRequest 1개</t>
         </is>
       </c>
-      <c r="G30" s="30" t="inlineStr">
+      <c r="G31" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H30" s="32" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="H31" s="32" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>edi_code</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D32" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest.medicationCodeableConcept.coding</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>system = 심평원 EDI 제품코드</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H31" s="15" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="inlineStr">
-        <is>
-          <t>raw_name</t>
-        </is>
-      </c>
-      <c r="D32" s="32" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E32" s="32" t="inlineStr">
-        <is>
-          <t>MedicationRequest.medicationCodeableConcept.text</t>
-        </is>
-      </c>
-      <c r="F32" s="32" t="inlineStr">
-        <is>
-          <t>OCR이 읽은 원문 약품명</t>
-        </is>
-      </c>
-      <c r="G32" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H32" s="32" t="inlineStr">
-        <is>
-          <t>매칭 실패해도 text는 남음</t>
-        </is>
-      </c>
+      <c r="H32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="30" t="inlineStr">
@@ -2023,64 +2020,68 @@
       </c>
       <c r="C33" s="32" t="inlineStr">
         <is>
+          <t>raw_name</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>MedicationRequest.medicationCodeableConcept.text</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>OCR이 읽은 원문 약품명</t>
+        </is>
+      </c>
+      <c r="G33" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H33" s="32" t="inlineStr">
+        <is>
+          <t>매칭 실패해도 text는 남음</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
           <t>dose_per_time</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>MedicationRequest.dosageInstruction.doseAndRate.doseQuantity</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr"/>
-      <c r="G33" s="30" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr"/>
+      <c r="G34" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H33" s="32" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>prescription_items</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>times_per_day</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>MedicationRequest.dosageInstruction.timing.repeat.frequency</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>period = 1, periodUnit = d</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="inlineStr"/>
+      <c r="H34" s="32" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -2095,7 +2096,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>total_days</t>
+          <t>times_per_day</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -2105,12 +2106,12 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
+          <t>MedicationRequest.dosageInstruction.timing.repeat.frequency</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>단위 d(일)</t>
+          <t>period = 1, periodUnit = d</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
@@ -2133,7 +2134,7 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>total_days</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
@@ -2143,12 +2144,12 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>MedicationRequest.dosageInstruction.timing.repeat.when</t>
+          <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>아침 식후 → PCM, 저녁 식후 → PCV, 취침 전 → HS 등 + text 원문</t>
+          <t>단위 d(일)</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
@@ -2171,158 +2172,154 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>MedicationRequest.dosageInstruction.timing.repeat.when</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>아침 식후 → PCM, 저녁 식후 → PCV, 취침 전 → HS 등 + text 원문</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>입력</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>prescription_items</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>MedicationRequest.dosageInstruction.patientInstruction</t>
         </is>
       </c>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>문장 목록 → 줄바꿈으로 이어 붙인 text</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="H38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>prescription_items</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>match_status · match_score</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr"/>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="F39" s="21" t="inlineStr"/>
+      <c r="G39" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
         <is>
           <t>약품 매칭 상태는 내부 처리 정보</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="34" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>입력</t>
         </is>
       </c>
-      <c r="B39" s="40" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>prescription_item_candidates</t>
         </is>
       </c>
-      <c r="C39" s="36" t="inlineStr">
+      <c r="C40" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="36" t="inlineStr">
+      <c r="E40" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F39" s="36" t="inlineStr"/>
-      <c r="G39" s="34" t="inlineStr">
+      <c r="F40" s="36" t="inlineStr"/>
+      <c r="G40" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H39" s="36" t="inlineStr">
+      <c r="H40" s="36" t="inlineStr">
         <is>
           <t>약품 매칭 후보 (내부 처리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>입력</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>health_checkups · checkup_results</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>DiagnosticReport · Observation</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>Observation.code / valueQuantity</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>검진 항목 코드 → Observation.code</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="inlineStr">
-        <is>
-          <t>보류 (REQ-015)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>분석</t>
+          <t>입력</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>analyses</t>
+          <t>health_checkups · checkup_results</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -2332,17 +2329,17 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>DiagnosticReport · Observation</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Observation.code / valueQuantity</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>분석 작업 1건 = Task 1개</t>
+          <t>검진 항목 코드 → Observation.code</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">
@@ -2352,7 +2349,7 @@
       </c>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>비동기 작업 상태를 Task로 표현</t>
+          <t>보류 (REQ-015)</t>
         </is>
       </c>
     </row>
@@ -2362,149 +2359,149 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B42" s="33" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>분석 작업 1건 = Task 1개</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>비동기 작업 상태를 Task로 표현</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>analyses</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>Task.status</t>
         </is>
       </c>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="F43" s="15" t="inlineStr">
         <is>
           <t>queued → requested / running → in-progress / done → completed / failed → failed</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H42" s="15" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>current_step · failed_step · retry_count · error_code</t>
         </is>
       </c>
-      <c r="D43" s="21" t="inlineStr">
+      <c r="D44" s="21" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="E43" s="21" t="inlineStr">
+      <c r="E44" s="21" t="inlineStr">
         <is>
           <t>Task.businessStatus · Task.statusReason</t>
         </is>
       </c>
-      <c r="F43" s="21" t="inlineStr"/>
-      <c r="G43" s="22" t="inlineStr">
+      <c r="F44" s="21" t="inlineStr"/>
+      <c r="G44" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H43" s="21" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="H44" s="21" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B44" s="35" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>analyses</t>
         </is>
       </c>
-      <c r="C44" s="36" t="inlineStr">
+      <c r="C45" s="36" t="inlineStr">
         <is>
           <t>user_birth_year</t>
         </is>
       </c>
-      <c r="D44" s="36" t="inlineStr">
+      <c r="D45" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E44" s="36" t="inlineStr">
+      <c r="E45" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F44" s="36" t="inlineStr"/>
-      <c r="G44" s="34" t="inlineStr">
+      <c r="F45" s="36" t="inlineStr"/>
+      <c r="G45" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H44" s="36" t="inlineStr">
+      <c r="H45" s="36" t="inlineStr">
         <is>
           <t>분석 시점 스냅샷 (내부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t>analysis_prescriptions</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>Task.input</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr">
-        <is>
-          <t>valueReference = MedicationRequest</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="inlineStr">
-        <is>
-          <t>분석에 넣은 처방 목록</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2513,7 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>analysis_diseases</t>
+          <t>analysis_prescriptions</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -2526,21 +2523,29 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr"/>
+          <t>Task.input</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>valueReference = MedicationRequest</t>
+        </is>
+      </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H46" s="15" t="inlineStr"/>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>분석에 넣은 처방 목록</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -2548,123 +2553,115 @@
           <t>분석</t>
         </is>
       </c>
-      <c r="B47" s="33" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>analysis_diseases</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr"/>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>analysis_diseases</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
           <t>origin</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>Condition.asserter</t>
         </is>
       </c>
-      <c r="F47" s="15" t="inlineStr">
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>prescription → 처방전에서 옴 / user → asserter = Patient (직접 선택)</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="G48" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H47" s="15" t="inlineStr">
+      <c r="H48" s="15" t="inlineStr">
         <is>
           <t>누가 주장한 질환인지 구분</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="30" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B48" s="38" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C48" s="32" t="inlineStr">
+      <c r="C49" s="32" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D48" s="39" t="inlineStr">
+      <c r="D49" s="39" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E48" s="32" t="inlineStr">
+      <c r="E49" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="F48" s="32" t="inlineStr">
+      <c r="F49" s="32" t="inlineStr">
         <is>
           <t>경고 1건 = DetectedIssue 1개</t>
         </is>
       </c>
-      <c r="G48" s="30" t="inlineStr">
+      <c r="G49" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H48" s="32" t="inlineStr">
+      <c r="H49" s="32" t="inlineStr">
         <is>
           <t>FHIR에 "약물 문제 감지" 전용 리소스가 있음 — 가장 잘 맞는 부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B49" s="33" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>warning_type</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>DetectedIssue.code</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
         </is>
       </c>
     </row>
@@ -2681,68 +2678,72 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
+          <t>warning_type</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>DetectedIssue.code</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>interaction → DRG / duplicate_* → DUPTHPY / dose_exceed → DOSEHIGH / age → AGE / elderly · pregnancy · polypharmacy → 자체 코드</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>HL7 v3 ActCode 후보 — 구현 시 코드 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue.severity</t>
         </is>
       </c>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>danger → high / caution → moderate / info → low</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G51" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="30" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>analysis_warnings</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>item_id_a · item_id_b</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue</t>
-        </is>
-      </c>
-      <c r="E51" s="32" t="inlineStr">
-        <is>
-          <t>DetectedIssue.implicated</t>
-        </is>
-      </c>
-      <c r="F51" s="32" t="inlineStr">
-        <is>
-          <t>Reference(MedicationRequest) 2개</t>
-        </is>
-      </c>
-      <c r="G51" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H51" s="32" t="inlineStr"/>
+      <c r="H51" s="15" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="30" t="inlineStr">
@@ -2757,142 +2758,142 @@
       </c>
       <c r="C52" s="32" t="inlineStr">
         <is>
+          <t>item_id_a · item_id_b</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue</t>
+        </is>
+      </c>
+      <c r="E52" s="32" t="inlineStr">
+        <is>
+          <t>DetectedIssue.implicated</t>
+        </is>
+      </c>
+      <c r="F52" s="32" t="inlineStr">
+        <is>
+          <t>Reference(MedicationRequest) 2개</t>
+        </is>
+      </c>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H52" s="32" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>analysis_warnings</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="D52" s="32" t="inlineStr">
+      <c r="D53" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E52" s="32" t="inlineStr">
+      <c r="E53" s="32" t="inlineStr">
         <is>
           <t>DetectedIssue.detail</t>
         </is>
       </c>
-      <c r="F52" s="32" t="inlineStr">
+      <c r="F53" s="32" t="inlineStr">
         <is>
           <t>DUR 금기 사유 원문</t>
         </is>
       </c>
-      <c r="G52" s="30" t="inlineStr">
+      <c r="G53" s="30" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="H52" s="32" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="H53" s="32" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B53" s="33" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>source · notice_date</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>DetectedIssue.reference</t>
         </is>
       </c>
-      <c r="F53" s="15" t="inlineStr">
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>식약처 고시 출처</t>
         </is>
       </c>
-      <c r="G53" s="16" t="inlineStr">
+      <c r="G54" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H53" s="15" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="H54" s="15" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
       </c>
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B55" s="37" t="inlineStr">
         <is>
           <t>analysis_warnings</t>
         </is>
       </c>
-      <c r="C54" s="21" t="inlineStr">
+      <c r="C55" s="21" t="inlineStr">
         <is>
           <t>summary · daily_total · max_daily</t>
         </is>
       </c>
-      <c r="D54" s="21" t="inlineStr">
+      <c r="D55" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
+      <c r="E55" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F54" s="21" t="inlineStr"/>
-      <c r="G54" s="22" t="inlineStr">
+      <c r="F55" s="21" t="inlineStr"/>
+      <c r="G55" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H54" s="21" t="inlineStr">
+      <c r="H55" s="21" t="inlineStr">
         <is>
           <t>화면 문장 · 용량 계산값</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="34" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B55" s="40" t="inlineStr">
-        <is>
-          <t>guides</t>
-        </is>
-      </c>
-      <c r="C55" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="36" t="inlineStr"/>
-      <c r="G55" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H55" s="36" t="inlineStr">
-        <is>
-          <t>AI 생성 안내문 (의료 기록 아님). 필요하면 DocumentReference로 보관</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2905,7 @@
       </c>
       <c r="B56" s="40" t="inlineStr">
         <is>
-          <t>feedbacks</t>
+          <t>guides</t>
         </is>
       </c>
       <c r="C56" s="36" t="inlineStr">
@@ -2930,19 +2931,19 @@
       </c>
       <c r="H56" s="36" t="inlineStr">
         <is>
-          <t>서비스 피드백</t>
+          <t>AI 생성 안내문 (의료 기록 아님). 필요하면 DocumentReference로 보관</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>챗봇</t>
+          <t>분석</t>
         </is>
       </c>
       <c r="B57" s="40" t="inlineStr">
         <is>
-          <t>chat_sessions</t>
+          <t>feedbacks</t>
         </is>
       </c>
       <c r="C57" s="36" t="inlineStr">
@@ -2968,45 +2969,45 @@
       </c>
       <c r="H57" s="36" t="inlineStr">
         <is>
+          <t>서비스 피드백</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>챗봇</t>
+        </is>
+      </c>
+      <c r="B58" s="40" t="inlineStr">
+        <is>
+          <t>chat_sessions</t>
+        </is>
+      </c>
+      <c r="C58" s="36" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="36" t="inlineStr"/>
+      <c r="G58" s="34" t="inlineStr">
+        <is>
+          <t>FHIR 외</t>
+        </is>
+      </c>
+      <c r="H58" s="36" t="inlineStr">
+        <is>
           <t>대화 묶음 (내부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>챗봇</t>
-        </is>
-      </c>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>chat_messages</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="F58" s="15" t="inlineStr"/>
-      <c r="G58" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H58" s="15" t="inlineStr">
-        <is>
-          <t>의료 기록으로 보관할 필요가 생길 때만</t>
         </is>
       </c>
     </row>
@@ -3016,24 +3017,24 @@
           <t>챗봇</t>
         </is>
       </c>
-      <c r="B59" s="33" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>chat_messages</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>role · content · created_at</t>
-        </is>
-      </c>
-      <c r="D59" s="15" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>Communication.sender · payload.contentString · sent</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr"/>
@@ -3042,83 +3043,83 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H59" s="15" t="inlineStr"/>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>의료 기록으로 보관할 필요가 생길 때만</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
+          <t>챗봇</t>
+        </is>
+      </c>
+      <c r="B60" s="33" t="inlineStr">
+        <is>
+          <t>chat_messages</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>role · content · created_at</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>Communication.sender · payload.contentString · sent</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="inlineStr"/>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B60" s="19" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>recommendations</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>CarePlan</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
         <is>
           <t>CarePlan.activity</t>
         </is>
       </c>
-      <c r="F60" s="15" t="inlineStr">
+      <c r="F61" s="15" t="inlineStr">
         <is>
           <t>추천 1개 = activity 1개 (status = not-started)</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="G61" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H60" s="15" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="30" t="inlineStr">
-        <is>
-          <t>실천·보상</t>
-        </is>
-      </c>
-      <c r="B61" s="38" t="inlineStr">
-        <is>
-          <t>habit_goals</t>
-        </is>
-      </c>
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D61" s="39" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="E61" s="32" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="F61" s="32" t="inlineStr"/>
-      <c r="G61" s="30" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-      <c r="H61" s="32" t="inlineStr">
-        <is>
-          <t>FHIR Goal = 환자 건강 목표</t>
-        </is>
-      </c>
+      <c r="H61" s="15" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="30" t="inlineStr">
@@ -3126,24 +3127,24 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B62" s="31" t="inlineStr">
+      <c r="B62" s="38" t="inlineStr">
         <is>
           <t>habit_goals</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D62" s="32" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D62" s="39" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>Goal.description.text</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="F62" s="32" t="inlineStr"/>
@@ -3152,7 +3153,11 @@
           <t>일치</t>
         </is>
       </c>
-      <c r="H62" s="32" t="inlineStr"/>
+      <c r="H62" s="32" t="inlineStr">
+        <is>
+          <t>FHIR Goal = 환자 건강 목표</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="30" t="inlineStr">
@@ -3167,7 +3172,7 @@
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>target_value · unit</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D63" s="32" t="inlineStr">
@@ -3177,7 +3182,7 @@
       </c>
       <c r="E63" s="32" t="inlineStr">
         <is>
-          <t>Goal.target.detailQuantity</t>
+          <t>Goal.description.text</t>
         </is>
       </c>
       <c r="F63" s="32" t="inlineStr"/>
@@ -3201,7 +3206,7 @@
       </c>
       <c r="C64" s="32" t="inlineStr">
         <is>
-          <t>start_date · end_date</t>
+          <t>target_value · unit</t>
         </is>
       </c>
       <c r="D64" s="32" t="inlineStr">
@@ -3211,7 +3216,7 @@
       </c>
       <c r="E64" s="32" t="inlineStr">
         <is>
-          <t>Goal.startDate · Goal.target.dueDate</t>
+          <t>Goal.target.detailQuantity</t>
         </is>
       </c>
       <c r="F64" s="32" t="inlineStr"/>
@@ -3223,42 +3228,38 @@
       <c r="H64" s="32" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="A65" s="30" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B65" s="33" t="inlineStr">
+      <c r="B65" s="31" t="inlineStr">
         <is>
           <t>habit_goals</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>start_date · end_date</t>
+        </is>
+      </c>
+      <c r="D65" s="32" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>Goal.lifecycleStatus</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>active → active / ended → completed</t>
-        </is>
-      </c>
-      <c r="G65" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="inlineStr"/>
+      <c r="E65" s="32" t="inlineStr">
+        <is>
+          <t>Goal.startDate · Goal.target.dueDate</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr"/>
+      <c r="G65" s="30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+      <c r="H65" s="32" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -3266,29 +3267,29 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B66" s="19" t="inlineStr">
-        <is>
-          <t>habit_records</t>
+      <c r="B66" s="33" t="inlineStr">
+        <is>
+          <t>habit_goals</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>Observation</t>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>Goal</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Goal.lifecycleStatus</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
+          <t>active → active / ended → completed</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr">
@@ -3304,105 +3305,109 @@
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B67" s="33" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>habit_records</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>기록 1건 = Observation 1개 (focus = Goal)</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>실천·보상</t>
+        </is>
+      </c>
+      <c r="B68" s="33" t="inlineStr">
+        <is>
+          <t>habit_records</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
           <t>value · completed · record_date</t>
         </is>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
       </c>
-      <c r="E67" s="15" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr">
         <is>
           <t>Observation.valueQuantity / valueBoolean · effectiveDateTime</t>
         </is>
       </c>
-      <c r="F67" s="15" t="inlineStr"/>
-      <c r="G67" s="16" t="inlineStr">
+      <c r="F68" s="15" t="inlineStr"/>
+      <c r="G68" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H67" s="15" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="34" t="inlineStr">
+      <c r="H68" s="15" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="34" t="inlineStr">
         <is>
           <t>실천·보상</t>
         </is>
       </c>
-      <c r="B68" s="40" t="inlineStr">
+      <c r="B69" s="40" t="inlineStr">
         <is>
           <t>rewards</t>
         </is>
       </c>
-      <c r="C68" s="36" t="inlineStr">
+      <c r="C69" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E68" s="36" t="inlineStr">
+      <c r="E69" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F68" s="36" t="inlineStr"/>
-      <c r="G68" s="34" t="inlineStr">
+      <c r="F69" s="36" t="inlineStr"/>
+      <c r="G69" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H68" s="36" t="inlineStr">
+      <c r="H69" s="36" t="inlineStr">
         <is>
           <t>포인트 (서비스 보상)</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>drug_products</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr">
-        <is>
-          <t>Medication</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr"/>
-      <c r="G69" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -3410,31 +3415,27 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B70" s="33" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>drug_products</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>edi_code</t>
-        </is>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
         <is>
           <t>Medication</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Medication.code.coding</t>
-        </is>
-      </c>
-      <c r="F70" s="15" t="inlineStr">
-        <is>
-          <t>system = 심평원 EDI 제품코드</t>
-        </is>
-      </c>
+          <t>Medication</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr"/>
       <c r="G70" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3455,7 +3456,7 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>ingr_code</t>
+          <t>edi_code</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
@@ -3465,12 +3466,12 @@
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Medication.ingredient.itemCodeableConcept</t>
+          <t>Medication.code.coding</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>system = 심평원 주성분코드</t>
+          <t>system = 심평원 EDI 제품코드</t>
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr">
@@ -3493,20 +3494,24 @@
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>entp_name</t>
+          <t>ingr_code</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>Organization</t>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Medication.manufacturer → Organization.name</t>
-        </is>
-      </c>
-      <c r="F72" s="15" t="inlineStr"/>
+          <t>Medication.ingredient.itemCodeableConcept</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>system = 심평원 주성분코드</t>
+        </is>
+      </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3527,17 +3532,17 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>spec_value · spec_unit</t>
+          <t>entp_name</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>Medication</t>
+          <t>Organization</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>Medication.ingredient.strength</t>
+          <t>Medication.manufacturer → Organization.name</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr"/>
@@ -3554,24 +3559,24 @@
           <t>마스터</t>
         </is>
       </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>drug_ingredients</t>
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t>drug_products</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D74" s="14" t="inlineStr">
-        <is>
-          <t>Substance</t>
+          <t>spec_value · spec_unit</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Medication</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Substance.code</t>
+          <t>Medication.ingredient.strength</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr"/>
@@ -3590,7 +3595,7 @@
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>drug_details</t>
+          <t>drug_ingredients</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
@@ -3600,29 +3605,21 @@
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>MedicationKnowledge</t>
+          <t>Substance</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>MedicationKnowledge</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="inlineStr">
-        <is>
-          <t>효능효과 · 용법용량 · 주의사항</t>
-        </is>
-      </c>
+          <t>Substance.code</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr"/>
       <c r="G75" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H75" s="15" t="inlineStr">
-        <is>
-          <t>RAG 검색 원문</t>
-        </is>
-      </c>
+      <c r="H75" s="15" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -3632,7 +3629,7 @@
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>dur_interaction · dur_interaction_exception</t>
+          <t>drug_details</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
@@ -3642,17 +3639,17 @@
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition (R5)</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.interaction</t>
+          <t>MedicationKnowledge</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>type = interaction</t>
+          <t>효능효과 · 용법용량 · 주의사항</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
@@ -3662,7 +3659,7 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>R4에는 전용 리소스 없음 — R5 참고</t>
+          <t>RAG 검색 원문</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3671,7 @@
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
+          <t>dur_interaction · dur_interaction_exception</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
@@ -3689,12 +3686,12 @@
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>ClinicalUseDefinition.contraindication</t>
+          <t>ClinicalUseDefinition.interaction</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>type = contraindication, population = 나이 · 임부</t>
+          <t>type = interaction</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
@@ -3704,7 +3701,7 @@
       </c>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>R5 참고</t>
+          <t>R4에는 전용 리소스 없음 — R5 참고</t>
         </is>
       </c>
     </row>
@@ -3716,111 +3713,115 @@
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
+          <t>dur_elderly · dur_age_limit · dur_pregnancy</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>ClinicalUseDefinition (R5)</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>ClinicalUseDefinition.contraindication</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>type = contraindication, population = 나이 · 임부</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>R5 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
           <t>dur_dose_limit</t>
         </is>
       </c>
-      <c r="C78" s="15" t="inlineStr">
+      <c r="C79" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr">
+      <c r="D79" s="14" t="inlineStr">
         <is>
           <t>MedicationKnowledge</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr">
+      <c r="E79" s="15" t="inlineStr">
         <is>
           <t>MedicationKnowledge.administrationGuidelines.dosage</t>
         </is>
       </c>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="F79" s="15" t="inlineStr">
         <is>
           <t>1일 최대 투여량</t>
         </is>
       </c>
-      <c r="G78" s="16" t="inlineStr">
+      <c r="G79" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H78" s="15" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="34" t="inlineStr">
+      <c r="H79" s="15" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="34" t="inlineStr">
         <is>
           <t>마스터</t>
         </is>
       </c>
-      <c r="B79" s="40" t="inlineStr">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t>dup_ingredient · dup_efficacy</t>
         </is>
       </c>
-      <c r="C79" s="36" t="inlineStr">
+      <c r="C80" s="36" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D80" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E79" s="36" t="inlineStr">
+      <c r="E80" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F79" s="36" t="inlineStr"/>
-      <c r="G79" s="34" t="inlineStr">
+      <c r="F80" s="36" t="inlineStr"/>
+      <c r="G80" s="34" t="inlineStr">
         <is>
           <t>FHIR 외</t>
         </is>
       </c>
-      <c r="H79" s="36" t="inlineStr">
+      <c r="H80" s="36" t="inlineStr">
         <is>
           <t>국내 DUR 중복 점검 규칙</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t>마스터</t>
-        </is>
-      </c>
-      <c r="B80" s="19" t="inlineStr">
-        <is>
-          <t>diseases</t>
-        </is>
-      </c>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="inlineStr">
-        <is>
-          <t>CodeSystem</t>
-        </is>
-      </c>
-      <c r="E80" s="15" t="inlineStr">
-        <is>
-          <t>CodeSystem.concept</t>
-        </is>
-      </c>
-      <c r="F80" s="15" t="inlineStr">
-        <is>
-          <t>KCD 상병 코드 목록</t>
-        </is>
-      </c>
-      <c r="G80" s="16" t="inlineStr">
-        <is>
-          <t>변환</t>
-        </is>
-      </c>
-      <c r="H80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -3830,7 +3831,7 @@
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>checkup_items</t>
+          <t>diseases</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
@@ -3850,7 +3851,7 @@
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>건강검진 검사항목 코드 목록</t>
+          <t>KCD 상병 코드 목록</t>
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr">
@@ -3858,11 +3859,7 @@
           <t>변환</t>
         </is>
       </c>
-      <c r="H81" s="15" t="inlineStr">
-        <is>
-          <t>보류</t>
-        </is>
-      </c>
+      <c r="H81" s="15" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -3872,7 +3869,7 @@
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
+          <t>checkup_items</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -3882,15 +3879,19 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>PlanDefinition</t>
+          <t>CodeSystem</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>PlanDefinition.action</t>
-        </is>
-      </c>
-      <c r="F82" s="15" t="inlineStr"/>
+          <t>CodeSystem.concept</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>건강검진 검사항목 코드 목록</t>
+        </is>
+      </c>
       <c r="G82" s="16" t="inlineStr">
         <is>
           <t>변환</t>
@@ -3898,7 +3899,7 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
+          <t>보류</t>
         </is>
       </c>
     </row>
@@ -3910,113 +3911,113 @@
       </c>
       <c r="B83" s="19" t="inlineStr">
         <is>
+          <t>lifestyle_guides · lifestyle_guide_actions · lifestyle_medication_links</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>(테이블)</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>PlanDefinition</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>PlanDefinition.action</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr"/>
+      <c r="G83" s="16" t="inlineStr">
+        <is>
+          <t>변환</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>자체 생활습관 지식 베이스. 실천 항목 1개 = PlanDefinition.action 1개</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>마스터</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
           <t>lifestyle_guide_sources</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
+      <c r="C84" s="15" t="inlineStr">
         <is>
           <t>(테이블)</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
+      <c r="D84" s="14" t="inlineStr">
         <is>
           <t>DocumentReference / Citation (R5)</t>
         </is>
       </c>
-      <c r="E83" s="15" t="inlineStr">
+      <c r="E84" s="15" t="inlineStr">
         <is>
           <t>PlanDefinition.relatedArtifact</t>
         </is>
       </c>
-      <c r="F83" s="15" t="inlineStr">
+      <c r="F84" s="15" t="inlineStr">
         <is>
           <t>type = citation · display = 문서명 · url · citation = 기관 · 발행일</t>
         </is>
       </c>
-      <c r="G83" s="16" t="inlineStr">
+      <c r="G84" s="16" t="inlineStr">
         <is>
           <t>변환</t>
         </is>
       </c>
-      <c r="H83" s="15" t="inlineStr">
+      <c r="H84" s="15" t="inlineStr">
         <is>
           <t>v1.2 · R4는 relatedArtifact로 출처 표시</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="22" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="22" t="inlineStr">
         <is>
           <t>마스터</t>
         </is>
       </c>
-      <c r="B84" s="37" t="inlineStr">
+      <c r="B85" s="37" t="inlineStr">
         <is>
           <t>lifestyle_medication_links</t>
         </is>
       </c>
-      <c r="C84" s="21" t="inlineStr">
+      <c r="C85" s="21" t="inlineStr">
         <is>
           <t>requires_clinician · goal_eligible</t>
         </is>
       </c>
-      <c r="D84" s="21" t="inlineStr">
+      <c r="D85" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E84" s="21" t="inlineStr">
+      <c r="E85" s="21" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="F84" s="21" t="inlineStr"/>
-      <c r="G84" s="22" t="inlineStr">
+      <c r="F85" s="21" t="inlineStr"/>
+      <c r="G85" s="22" t="inlineStr">
         <is>
           <t>확장</t>
         </is>
       </c>
-      <c r="H84" s="21" t="inlineStr">
+      <c r="H85" s="21" t="inlineStr">
         <is>
           <t>v1.2 · 서비스 표시 규칙</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="34" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="B85" s="40" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="C85" s="36" t="inlineStr">
-        <is>
-          <t>(테이블)</t>
-        </is>
-      </c>
-      <c r="D85" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E85" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" s="36" t="n"/>
-      <c r="G85" s="34" t="inlineStr">
-        <is>
-          <t>FHIR 외</t>
-        </is>
-      </c>
-      <c r="H85" s="36" t="inlineStr">
-        <is>
-          <t>미리 저장해 두는 AI 생성 약 안내문 (의료 기록 아님). guides와 같은 이유로 FHIR 대응 없음</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4038,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7089,84 +7090,6 @@
         </is>
       </c>
       <c r="E158" s="10" t="n"/>
-    </row>
-    <row r="159" hidden="1" outlineLevel="1">
-      <c r="A159" s="10" t="n"/>
-      <c r="B159" s="10" t="inlineStr">
-        <is>
-          <t>사용자 / users.nickname — 필드 삭제</t>
-        </is>
-      </c>
-      <c r="C159" s="10" t="inlineStr">
-        <is>
-          <t>nickname varchar(50) · N — 선택 입력. 홈 인사말용</t>
-        </is>
-      </c>
-      <c r="D159" s="10" t="inlineStr">
-        <is>
-          <t>삭제
-사유: 홈 인사말을 뺌(3회차 멘토링 · 10/7 회의). 인사말용 별명이 쓸 곳이 없어 최소 수집 원칙에 맞춰 뺌 (10/14 팀 합의 · #96). 가입 · 로그인 · 내 정보 응답에서도 뺌</t>
-        </is>
-      </c>
-      <c r="E159" s="10" t="n"/>
-    </row>
-    <row r="160" hidden="1" outlineLevel="1">
-      <c r="A160" s="10" t="n"/>
-      <c r="B160" s="10" t="inlineStr">
-        <is>
-          <t>FHIR 대응 탭 — users.nickname 행 삭제</t>
-        </is>
-      </c>
-      <c r="C160" s="10" t="inlineStr">
-        <is>
-          <t>80행 — nickname → Patient.name.text</t>
-        </is>
-      </c>
-      <c r="D160" s="10" t="inlineStr">
-        <is>
-          <t>79행 — 칸이 없어져 대응 행도 뺌</t>
-        </is>
-      </c>
-      <c r="E160" s="10" t="n"/>
-    </row>
-    <row r="161" hidden="1" outlineLevel="1">
-      <c r="A161" s="10" t="n"/>
-      <c r="B161" s="10" t="inlineStr">
-        <is>
-          <t>분석 / drug_guides — 테이블 신규</t>
-        </is>
-      </c>
-      <c r="C161" s="10" t="inlineStr">
-        <is>
-          <t>(없음) — 안내문은 분석 때마다 guides에 만들었음</t>
-        </is>
-      </c>
-      <c r="D161" s="10" t="inlineStr">
-        <is>
-          <t>필드 10개: edi_code(PK), content, evidence_ids, prompt_ver, model_name, review_status, reviewed_by, reviewed_at, created_at, updated_at
-사유: 멘토링 4회차(10/13) · 10/14 팀 합의 — 안내문을 약 단위로 미리 저장하고 사람이 확인한 것만 분석에 씀. 근거 번호와 출처를 같이 저장해 챗봇이 그대로 씀</t>
-        </is>
-      </c>
-      <c r="E161" s="10" t="n"/>
-    </row>
-    <row r="162" hidden="1" outlineLevel="1">
-      <c r="A162" s="10" t="n"/>
-      <c r="B162" s="10" t="inlineStr">
-        <is>
-          <t>FHIR 대응 탭 — drug_guides 행 추가</t>
-        </is>
-      </c>
-      <c r="C162" s="10" t="inlineStr">
-        <is>
-          <t>79행</t>
-        </is>
-      </c>
-      <c r="D162" s="10" t="inlineStr">
-        <is>
-          <t>80행 — drug_guides (테이블) · FHIR 외 (guides와 같음)</t>
-        </is>
-      </c>
-      <c r="E162" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7449,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7739,30 +7662,30 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>birth_year</t>
+          <t>nickname</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>출생연도</t>
+          <t>이름 (별명)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr"/>
       <c r="G8" s="21" t="inlineStr"/>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t>생년월일 대신 출생연도만 (최소 수집) · 노인주의 · 연령금기 판정</t>
+          <t>선택 입력. 홈 인사말용</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -7795,17 +7718,17 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>birth_year</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>성별</t>
+          <t>출생연도</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>varchar(1)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr"/>
@@ -7818,85 +7741,81 @@
       <c r="I9" s="21" t="inlineStr"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
+          <t>생년월일 대신 출생연도만 (최소 수집) · 노인주의 · 연령금기 판정</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>CM-01~07 · A-1~3 · U-1~3</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>성별</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>varchar(1)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
           <t>M / F</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>CM-01~07 · A-1~3 · U-1~3</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M10" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N9" s="21" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>회원</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>failed_login_count</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>로그인 실패 횟수</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>smallint</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="inlineStr"/>
-      <c r="G10" s="24" t="inlineStr"/>
-      <c r="H10" s="25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="24" t="inlineStr">
-        <is>
-          <t>5회 실패 시 잠금 (CM-01-E1)</t>
-        </is>
-      </c>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>CM-01~07 · A-1~3 · U-1~3</t>
-        </is>
-      </c>
-      <c r="L10" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M10" s="25" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N10" s="24" t="inlineStr"/>
+      <c r="N10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
@@ -7911,17 +7830,17 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>locked_until</t>
+          <t>failed_login_count</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>잠금 해제 시각</t>
+          <t>로그인 실패 횟수</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr"/>
@@ -7931,252 +7850,252 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr"/>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
+          <t>5회 실패 시 잠금 (CM-01-E1)</t>
+        </is>
+      </c>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>CM-01~07 · A-1~3 · U-1~3</t>
+        </is>
+      </c>
+      <c r="L11" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M11" s="25" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N11" s="24" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>locked_until</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>잠금 해제 시각</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr"/>
+      <c r="G12" s="24" t="inlineStr"/>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr"/>
+      <c r="J12" s="24" t="inlineStr">
+        <is>
           <t>잠금 해제 시각 (CM-01-E2)</t>
         </is>
       </c>
-      <c r="K11" s="24" t="inlineStr">
+      <c r="K12" s="24" t="inlineStr">
         <is>
           <t>CM-01~07 · A-1~3 · U-1~3</t>
         </is>
       </c>
-      <c r="L11" s="25" t="inlineStr">
+      <c r="L12" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M11" s="25" t="inlineStr">
+      <c r="M12" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N11" s="24" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="N12" s="24" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>생성 일시</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="15" t="inlineStr"/>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr"/>
+      <c r="G13" s="15" t="inlineStr"/>
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr"/>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr"/>
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>CM-01~07 · A-1~3 · U-1~3</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>기존</t>
         </is>
       </c>
-      <c r="M12" s="16" t="inlineStr">
+      <c r="M13" s="16" t="inlineStr">
         <is>
           <t>v0.1</t>
         </is>
       </c>
-      <c r="N12" s="15" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="N13" s="15" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>수정 일시</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr"/>
-      <c r="G13" s="24" t="inlineStr"/>
-      <c r="H13" s="25" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr"/>
+      <c r="G14" s="24" t="inlineStr"/>
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I13" s="24" t="inlineStr"/>
-      <c r="J13" s="24" t="inlineStr"/>
-      <c r="K13" s="24" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr"/>
+      <c r="J14" s="24" t="inlineStr"/>
+      <c r="K14" s="24" t="inlineStr">
         <is>
           <t>CM-01~07 · A-1~3 · U-1~3</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L14" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M14" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N13" s="24" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="N14" s="24" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>deleted_at</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>탈퇴 일시</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr"/>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t>탈퇴 시 개인정보 파기 후 시각만 남김 (CM-07)</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="K15" s="21" t="inlineStr">
         <is>
           <t>CM-01~07 · A-1~3 · U-1~3</t>
         </is>
       </c>
-      <c r="L14" s="22" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>수정</t>
         </is>
       </c>
-      <c r="M14" s="22" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>user_consents</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>동의 기록</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr"/>
-      <c r="H15" s="25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr"/>
-      <c r="J15" s="24" t="inlineStr"/>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
-        </is>
-      </c>
-      <c r="L15" s="25" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t>v1.0</t>
-        </is>
-      </c>
-      <c r="N15" s="24" t="inlineStr">
-        <is>
-          <t>v1.0 신규 · CM-02 가입 동의, CM-05 동의 내역</t>
-        </is>
-      </c>
+      <c r="N15" s="21" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
@@ -8191,12 +8110,12 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>사용자 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -8206,14 +8125,10 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>users.id</t>
-        </is>
-      </c>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr"/>
       <c r="H16" s="25" t="inlineStr">
         <is>
           <t>Y</t>
@@ -8236,7 +8151,11 @@
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N16" s="24" t="inlineStr"/>
+      <c r="N16" s="24" t="inlineStr">
+        <is>
+          <t>v1.0 신규 · CM-02 가입 동의, CM-05 동의 내역</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
@@ -8251,32 +8170,36 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>consent_type</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>동의 종류</t>
+          <t>사용자 ID</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="inlineStr"/>
-      <c r="G17" s="24" t="inlineStr"/>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr"/>
-      <c r="J17" s="24" t="inlineStr">
-        <is>
-          <t>terms / privacy / sensitive_health</t>
-        </is>
-      </c>
+      <c r="J17" s="24" t="inlineStr"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
@@ -8307,17 +8230,17 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>consent_type</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>동의 여부</t>
+          <t>동의 종류</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="F18" s="25" t="inlineStr"/>
@@ -8328,7 +8251,11 @@
         </is>
       </c>
       <c r="I18" s="24" t="inlineStr"/>
-      <c r="J18" s="24" t="inlineStr"/>
+      <c r="J18" s="24" t="inlineStr">
+        <is>
+          <t>terms / privacy / sensitive_health</t>
+        </is>
+      </c>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
@@ -8359,24 +8286,24 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>agreed_at</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>동의 일시</t>
+          <t>동의 여부</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr"/>
       <c r="G19" s="24" t="inlineStr"/>
       <c r="H19" s="25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I19" s="24" t="inlineStr"/>
@@ -8411,12 +8338,12 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>withdrawn_at</t>
+          <t>agreed_at</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>철회 일시</t>
+          <t>동의 일시</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -8432,27 +8359,79 @@
         </is>
       </c>
       <c r="I20" s="24" t="inlineStr"/>
-      <c r="J20" s="24" t="inlineStr">
+      <c r="J20" s="24" t="inlineStr"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
+        </is>
+      </c>
+      <c r="L20" s="25" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="M20" s="25" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="N20" s="24" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>user_consents</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>동의 기록</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>withdrawn_at</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>철회 일시</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr"/>
+      <c r="G21" s="24" t="inlineStr"/>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr"/>
+      <c r="J21" s="24" t="inlineStr">
         <is>
           <t>철회 시각. sensitive_health 철회 시 업로드 · 분석 불가 (🟡 기존 기록 처리 팀 결정)</t>
         </is>
       </c>
-      <c r="K20" s="24" t="inlineStr">
+      <c r="K21" s="24" t="inlineStr">
         <is>
           <t>CM-02 · CM-05 · A-1 · U-4 · U-5</t>
         </is>
       </c>
-      <c r="L20" s="25" t="inlineStr">
+      <c r="L21" s="25" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="M20" s="25" t="inlineStr">
+      <c r="M21" s="25" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="N20" s="24" t="inlineStr">
+      <c r="N21" s="24" t="inlineStr">
         <is>
           <t>인덱스: (user_id, consent_type) [unique]</t>
         </is>
@@ -8514,6 +8493,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -11533,7 +11513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14089,570 +14069,6 @@
         </is>
       </c>
       <c r="N47" s="15" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>edi_code</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>약 코드</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>varchar(9)</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G48" s="15" t="n"/>
-      <c r="H48" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I48" s="15" t="n"/>
-      <c r="J48" s="15" t="inlineStr">
-        <is>
-          <t>약제급여목록 제품코드(EDI). 약 1개 = 1행. 급여목록에 없는 약은 행이 없음</t>
-        </is>
-      </c>
-      <c r="K48" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L48" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M48" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N48" s="15" t="inlineStr">
-        <is>
-          <t>멘토링 4회차(10/13) · 10/14 팀 합의. 약 단위로 미리 만들어 두고 사람이 확인한 것만 분석에 씀. 약 1개 = 1행 (약효분류 표로 만든 안내문과 허가정보 문장이 같은 표에 들어감)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>안내 내용 (JSON)</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="15" t="n"/>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="n"/>
-      <c r="J49" s="15" t="inlineStr">
-        <is>
-          <t>category · purpose · caution(문장을 줄바꿈으로 이은 문자열) · cautions(문장 배열) · source. 먹는 법은 처방마다 달라 여기 두지 않음</t>
-        </is>
-      </c>
-      <c r="K49" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L49" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M49" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N49" s="15" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>evidence_ids</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>근거 목록</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="n"/>
-      <c r="G50" s="15" t="n"/>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I50" s="15" t="n"/>
-      <c r="J50" s="15" t="inlineStr">
-        <is>
-          <t>[{kind: hira_class | drug_details, key, label, field(문장 번호), use(purpose · caution1~3), text(원문 문장)}] — 챗봇이 출처를 붙일 때 그대로 씀</t>
-        </is>
-      </c>
-      <c r="K50" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L50" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M50" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N50" s="15" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C51" s="15" t="inlineStr">
-        <is>
-          <t>prompt_ver</t>
-        </is>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>프롬프트 버전</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="n"/>
-      <c r="G51" s="15" t="n"/>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I51" s="15" t="n"/>
-      <c r="J51" s="15" t="inlineStr">
-        <is>
-          <t>규칙 표로 만든 것은 rule-v1, AI 문장은 med-v8</t>
-        </is>
-      </c>
-      <c r="K51" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L51" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M51" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N51" s="15" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>model_name</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>모델 이름</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="n"/>
-      <c r="G52" s="15" t="n"/>
-      <c r="H52" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I52" s="15" t="n"/>
-      <c r="J52" s="15" t="inlineStr">
-        <is>
-          <t>AI 없이 규칙 표로 만든 안내문은 null. 값이 있으면 허가정보 문장(AI가 쓰고 규칙으로 걸러 냄)</t>
-        </is>
-      </c>
-      <c r="K52" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L52" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M52" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N52" s="15" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C53" s="15" t="inlineStr">
-        <is>
-          <t>review_status</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>확인 상태</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
-          <t>varchar(20)</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="n"/>
-      <c r="G53" s="15" t="n"/>
-      <c r="H53" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="J53" s="15" t="inlineStr">
-        <is>
-          <t>draft / approved / rejected — 분석 때는 approved만 보여 줌 (멘토링 4회차 · 사람 확인 필수)</t>
-        </is>
-      </c>
-      <c r="K53" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L53" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M53" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N53" s="15" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>reviewed_by</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>확인한 사람</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>varchar(50)</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="15" t="n"/>
-      <c r="H54" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I54" s="15" t="n"/>
-      <c r="J54" s="15" t="n"/>
-      <c r="K54" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L54" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M54" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N54" s="15" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C55" s="15" t="inlineStr">
-        <is>
-          <t>reviewed_at</t>
-        </is>
-      </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>확인 일시</t>
-        </is>
-      </c>
-      <c r="E55" s="15" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="15" t="n"/>
-      <c r="H55" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I55" s="15" t="n"/>
-      <c r="J55" s="15" t="n"/>
-      <c r="K55" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L55" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M55" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N55" s="15" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>생성 일시</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="15" t="n"/>
-      <c r="H56" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I56" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J56" s="15" t="n"/>
-      <c r="K56" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L56" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M56" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N56" s="15" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="19" t="inlineStr">
-        <is>
-          <t>drug_guides</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>약 안내문 (사전 저장)</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>수정 일시</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="n"/>
-      <c r="G57" s="15" t="n"/>
-      <c r="H57" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="J57" s="15" t="n"/>
-      <c r="K57" s="15" t="inlineStr">
-        <is>
-          <t>RG-04 · R-4 · 챗봇 출처</t>
-        </is>
-      </c>
-      <c r="L57" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="M57" s="16" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="N57" s="15" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:N47"/>
